--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126836209</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836346</v>
+        <v>126837206</v>
       </c>
       <c r="B3" t="n">
-        <v>91487</v>
+        <v>78776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681265</v>
+        <v>680899</v>
       </c>
       <c r="R3" t="n">
-        <v>7087123</v>
+        <v>7087435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126837203</v>
+        <v>126836346</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681075</v>
+        <v>681265</v>
       </c>
       <c r="R4" t="n">
-        <v>7087404</v>
+        <v>7087123</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126837206</v>
+        <v>126837203</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680899</v>
+        <v>681075</v>
       </c>
       <c r="R5" t="n">
-        <v>7087435</v>
+        <v>7087404</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
         <v>126836318</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836422</v>
+        <v>126836434</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681560</v>
+        <v>681368</v>
       </c>
       <c r="R7" t="n">
-        <v>7087320</v>
+        <v>7087145</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,54 +1290,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836231</v>
+        <v>126836422</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681110</v>
+        <v>681560</v>
       </c>
       <c r="R8" t="n">
-        <v>7087306</v>
+        <v>7087320</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,32 +1391,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836434</v>
+        <v>126837209</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1435,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>681368</v>
+        <v>681166</v>
       </c>
       <c r="R9" t="n">
-        <v>7087145</v>
+        <v>7087366</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,12 +1476,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1501,45 +1492,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126837209</v>
+        <v>126836231</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>56853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>681166</v>
+        <v>681110</v>
       </c>
       <c r="R10" t="n">
-        <v>7087366</v>
+        <v>7087306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1586,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126840607</v>
+        <v>126836292</v>
       </c>
       <c r="B11" t="n">
-        <v>78772</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,37 +1613,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>681406</v>
+        <v>681520</v>
       </c>
       <c r="R11" t="n">
-        <v>7087115</v>
+        <v>7086769</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,40 +1670,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1717,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837081</v>
+        <v>126840607</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1728,34 +1714,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>681499</v>
+        <v>681406</v>
       </c>
       <c r="R12" t="n">
-        <v>7087039</v>
+        <v>7087115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,29 +1774,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1821,7 +1821,7 @@
         <v>126837205</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836292</v>
+        <v>126837081</v>
       </c>
       <c r="B14" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,34 +1930,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>681520</v>
+        <v>681499</v>
       </c>
       <c r="R14" t="n">
-        <v>7086769</v>
+        <v>7087039</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2023,7 +2023,7 @@
         <v>126840170</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>126840005</v>
       </c>
       <c r="B16" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,45 +2236,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126837065</v>
+        <v>126836219</v>
       </c>
       <c r="B17" t="n">
-        <v>78773</v>
+        <v>91295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>681401</v>
+        <v>681508</v>
       </c>
       <c r="R17" t="n">
-        <v>7087113</v>
+        <v>7087463</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,12 +2321,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836224</v>
+        <v>126838810</v>
       </c>
       <c r="B18" t="n">
-        <v>79603</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>681282</v>
+        <v>681251</v>
       </c>
       <c r="R18" t="n">
-        <v>7087132</v>
+        <v>7086940</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,12 +2422,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126838810</v>
+        <v>126836435</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,14 +2469,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>681251</v>
+        <v>681329</v>
       </c>
       <c r="R19" t="n">
-        <v>7086940</v>
+        <v>7087139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2523,12 +2523,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836435</v>
+        <v>126837065</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,34 +2550,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>681329</v>
+        <v>681401</v>
       </c>
       <c r="R20" t="n">
-        <v>7087139</v>
+        <v>7087113</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,12 +2624,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2640,32 +2640,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836219</v>
+        <v>126836224</v>
       </c>
       <c r="B21" t="n">
-        <v>91291</v>
+        <v>79607</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>681508</v>
+        <v>681282</v>
       </c>
       <c r="R21" t="n">
-        <v>7087463</v>
+        <v>7087132</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,7 +2744,7 @@
         <v>126837055</v>
       </c>
       <c r="B22" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>126836225</v>
       </c>
       <c r="B23" t="n">
-        <v>58516</v>
+        <v>58520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>126836432</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126837042</v>
+        <v>126837217</v>
       </c>
       <c r="B25" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3055,34 +3055,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>681238</v>
+        <v>681283</v>
       </c>
       <c r="R25" t="n">
-        <v>7087139</v>
+        <v>7087132</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3129,12 +3129,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126837217</v>
+        <v>126837042</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3156,34 +3156,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>681283</v>
+        <v>681238</v>
       </c>
       <c r="R26" t="n">
-        <v>7087132</v>
+        <v>7087139</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,12 +3230,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3246,10 +3246,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836214</v>
+        <v>126836427</v>
       </c>
       <c r="B27" t="n">
-        <v>96696</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>681496</v>
+        <v>681540</v>
       </c>
       <c r="R27" t="n">
-        <v>7087506</v>
+        <v>7087272</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,57 +3347,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126830094</v>
+        <v>126836214</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>681091</v>
+        <v>681496</v>
       </c>
       <c r="R28" t="n">
-        <v>7087426</v>
+        <v>7087506</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3427,40 +3415,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3471,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126839951</v>
+        <v>126836297</v>
       </c>
       <c r="B29" t="n">
-        <v>57817</v>
+        <v>78777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3482,21 +3459,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3506,10 +3483,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>681250</v>
+        <v>681585</v>
       </c>
       <c r="R29" t="n">
-        <v>7087112</v>
+        <v>7087270</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,12 +3533,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3572,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126836297</v>
+        <v>126839951</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>57821</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3583,21 +3560,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3607,10 +3584,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>681585</v>
+        <v>681250</v>
       </c>
       <c r="R30" t="n">
-        <v>7087270</v>
+        <v>7087112</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,12 +3634,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3673,45 +3650,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126836427</v>
+        <v>126830094</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>681540</v>
+        <v>681091</v>
       </c>
       <c r="R31" t="n">
-        <v>7087272</v>
+        <v>7087426</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3741,29 +3730,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3774,45 +3774,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836424</v>
+        <v>126837072</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>681515</v>
+        <v>681410</v>
       </c>
       <c r="R32" t="n">
-        <v>7087397</v>
+        <v>7087105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3878,7 +3878,7 @@
         <v>126837199</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126837194</v>
+        <v>126836425</v>
       </c>
       <c r="B34" t="n">
-        <v>57817</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>681159</v>
+        <v>681499</v>
       </c>
       <c r="R34" t="n">
         <v>7087381</v>
@@ -4061,12 +4061,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4077,45 +4077,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126837072</v>
+        <v>126836424</v>
       </c>
       <c r="B35" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>681410</v>
+        <v>681515</v>
       </c>
       <c r="R35" t="n">
-        <v>7087105</v>
+        <v>7087397</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4162,12 +4162,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4178,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126836425</v>
+        <v>126837194</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>57821</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>681499</v>
+        <v>681159</v>
       </c>
       <c r="R36" t="n">
         <v>7087381</v>
@@ -4263,12 +4263,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4279,32 +4279,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126837200</v>
+        <v>126836232</v>
       </c>
       <c r="B37" t="n">
-        <v>57654</v>
+        <v>56853</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4312,7 +4312,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>681264</v>
+        <v>681509</v>
       </c>
       <c r="R37" t="n">
-        <v>7087324</v>
+        <v>7087382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4360,11 +4360,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4377,12 +4372,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4393,32 +4388,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126836221</v>
+        <v>126837208</v>
       </c>
       <c r="B38" t="n">
-        <v>91291</v>
+        <v>78776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4428,10 +4423,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>681514</v>
+        <v>681315</v>
       </c>
       <c r="R38" t="n">
-        <v>7087467</v>
+        <v>7087155</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4478,12 +4473,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4494,32 +4489,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836232</v>
+        <v>126837200</v>
       </c>
       <c r="B39" t="n">
-        <v>56849</v>
+        <v>57658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4527,7 +4522,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4537,10 +4532,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>681509</v>
+        <v>681264</v>
       </c>
       <c r="R39" t="n">
-        <v>7087382</v>
+        <v>7087324</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4575,6 +4570,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4587,12 +4587,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4603,32 +4603,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126837208</v>
+        <v>126836221</v>
       </c>
       <c r="B40" t="n">
-        <v>78772</v>
+        <v>91295</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>681315</v>
+        <v>681514</v>
       </c>
       <c r="R40" t="n">
-        <v>7087155</v>
+        <v>7087467</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4688,12 +4688,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4704,45 +4704,59 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126836426</v>
+        <v>126836349</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>98481</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>681490</v>
+        <v>681163</v>
       </c>
       <c r="R41" t="n">
-        <v>7087351</v>
+        <v>7087254</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,59 +4819,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126836349</v>
+        <v>126840180</v>
       </c>
       <c r="B42" t="n">
-        <v>98477</v>
+        <v>80121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>681163</v>
+        <v>681446</v>
       </c>
       <c r="R42" t="n">
-        <v>7087254</v>
+        <v>7087459</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,29 +4890,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4920,10 +4934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126840180</v>
+        <v>126836426</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4931,37 +4945,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>681446</v>
+        <v>681490</v>
       </c>
       <c r="R43" t="n">
-        <v>7087459</v>
+        <v>7087351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4991,40 +5002,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5038,7 +5038,7 @@
         <v>126836218</v>
       </c>
       <c r="B44" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>126830813</v>
       </c>
       <c r="B45" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126837207</v>
       </c>
       <c r="B46" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>126837201</v>
       </c>
       <c r="B47" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>126836534</v>
       </c>
       <c r="B48" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>126837040</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>126837051</v>
       </c>
       <c r="B50" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5752,45 +5752,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126837066</v>
+        <v>126840200</v>
       </c>
       <c r="B51" t="n">
-        <v>78773</v>
+        <v>91491</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>681269</v>
+        <v>681091</v>
       </c>
       <c r="R51" t="n">
-        <v>7087084</v>
+        <v>7087431</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5820,29 +5823,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5856,7 +5870,7 @@
         <v>126836423</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5954,48 +5968,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126840200</v>
+        <v>126837204</v>
       </c>
       <c r="B53" t="n">
-        <v>91487</v>
+        <v>80121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>681091</v>
+        <v>681057</v>
       </c>
       <c r="R53" t="n">
-        <v>7087431</v>
+        <v>7087434</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6025,40 +6036,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6069,10 +6069,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126837204</v>
+        <v>126837066</v>
       </c>
       <c r="B54" t="n">
-        <v>80117</v>
+        <v>78777</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6080,34 +6080,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>681057</v>
+        <v>681269</v>
       </c>
       <c r="R54" t="n">
-        <v>7087434</v>
+        <v>7087084</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6154,12 +6154,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6173,7 +6173,7 @@
         <v>126837237</v>
       </c>
       <c r="B55" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6271,45 +6271,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126836496</v>
+        <v>126837080</v>
       </c>
       <c r="B56" t="n">
-        <v>98360</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>681155</v>
+        <v>681442</v>
       </c>
       <c r="R56" t="n">
-        <v>7087260</v>
+        <v>7086944</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6356,12 +6356,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6372,32 +6372,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126836421</v>
+        <v>126836496</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>98364</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>681572</v>
+        <v>681155</v>
       </c>
       <c r="R57" t="n">
-        <v>7087305</v>
+        <v>7087260</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126837080</v>
+        <v>126836421</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6504,14 +6504,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>681442</v>
+        <v>681572</v>
       </c>
       <c r="R58" t="n">
-        <v>7086944</v>
+        <v>7087305</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6558,12 +6558,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6574,32 +6574,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126836431</v>
+        <v>126837211</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>681443</v>
+        <v>681207</v>
       </c>
       <c r="R59" t="n">
-        <v>7087186</v>
+        <v>7087379</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6659,12 +6659,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6675,32 +6675,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126837230</v>
+        <v>126837210</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>680902</v>
+        <v>681199</v>
       </c>
       <c r="R60" t="n">
-        <v>7087430</v>
+        <v>7087367</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6776,10 +6776,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126837196</v>
+        <v>126836431</v>
       </c>
       <c r="B61" t="n">
-        <v>57817</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6787,21 +6787,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>681047</v>
+        <v>681443</v>
       </c>
       <c r="R61" t="n">
-        <v>7087442</v>
+        <v>7087186</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6861,12 +6861,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6877,32 +6877,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126836275</v>
+        <v>126837230</v>
       </c>
       <c r="B62" t="n">
-        <v>97321</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>681493</v>
+        <v>680902</v>
       </c>
       <c r="R62" t="n">
-        <v>7087510</v>
+        <v>7087430</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,12 +6962,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6978,32 +6978,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126837211</v>
+        <v>126837196</v>
       </c>
       <c r="B63" t="n">
-        <v>98443</v>
+        <v>57821</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>681207</v>
+        <v>681047</v>
       </c>
       <c r="R63" t="n">
-        <v>7087379</v>
+        <v>7087442</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7079,32 +7079,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126837210</v>
+        <v>126836275</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>97325</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>681199</v>
+        <v>681493</v>
       </c>
       <c r="R64" t="n">
-        <v>7087367</v>
+        <v>7087510</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,12 +7164,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7183,7 +7183,7 @@
         <v>126837067</v>
       </c>
       <c r="B65" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>126836294</v>
       </c>
       <c r="B66" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7382,32 +7382,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126837216</v>
+        <v>126836274</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>97325</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>681451</v>
+        <v>681531</v>
       </c>
       <c r="R67" t="n">
-        <v>7087136</v>
+        <v>7087468</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7467,12 +7467,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7483,10 +7483,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126837215</v>
+        <v>126836299</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>681516</v>
+        <v>681313</v>
       </c>
       <c r="R68" t="n">
-        <v>7087367</v>
+        <v>7087136</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7568,12 +7568,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7584,10 +7584,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126830801</v>
+        <v>126837064</v>
       </c>
       <c r="B69" t="n">
-        <v>78772</v>
+        <v>78777</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7595,34 +7595,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>681063</v>
+        <v>681464</v>
       </c>
       <c r="R69" t="n">
-        <v>7087438</v>
+        <v>7087062</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7652,19 +7652,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7679,12 +7669,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7695,10 +7685,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126836208</v>
+        <v>126837216</v>
       </c>
       <c r="B70" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7706,21 +7696,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7730,10 +7720,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>681523</v>
+        <v>681451</v>
       </c>
       <c r="R70" t="n">
-        <v>7086816</v>
+        <v>7087136</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7780,12 +7770,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7796,10 +7786,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126836299</v>
+        <v>126837215</v>
       </c>
       <c r="B71" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7807,21 +7797,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7831,10 +7821,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>681313</v>
+        <v>681516</v>
       </c>
       <c r="R71" t="n">
-        <v>7087136</v>
+        <v>7087367</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7881,12 +7871,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7897,45 +7887,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126837064</v>
+        <v>126836220</v>
       </c>
       <c r="B72" t="n">
-        <v>78773</v>
+        <v>91295</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>681464</v>
+        <v>681510</v>
       </c>
       <c r="R72" t="n">
-        <v>7087062</v>
+        <v>7087465</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7982,12 +7972,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7998,45 +7988,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126836220</v>
+        <v>126830801</v>
       </c>
       <c r="B73" t="n">
-        <v>91291</v>
+        <v>78776</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>681510</v>
+        <v>681063</v>
       </c>
       <c r="R73" t="n">
-        <v>7087465</v>
+        <v>7087438</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8066,9 +8056,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8083,12 +8083,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8099,32 +8099,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126836274</v>
+        <v>126836208</v>
       </c>
       <c r="B74" t="n">
-        <v>97321</v>
+        <v>79636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>681531</v>
+        <v>681523</v>
       </c>
       <c r="R74" t="n">
-        <v>7087468</v>
+        <v>7086816</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126828689</v>
+        <v>126840611</v>
       </c>
       <c r="B75" t="n">
-        <v>57654</v>
+        <v>78777</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8211,46 +8211,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>681562</v>
+        <v>681406</v>
       </c>
       <c r="R75" t="n">
-        <v>7087373</v>
+        <v>7087115</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8282,7 +8273,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8292,7 +8283,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8301,6 +8292,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8323,10 +8315,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126837041</v>
+        <v>126838812</v>
       </c>
       <c r="B76" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8334,34 +8326,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>681269</v>
+        <v>681315</v>
       </c>
       <c r="R76" t="n">
-        <v>7087084</v>
+        <v>7086965</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8408,12 +8400,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8424,10 +8416,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126838812</v>
+        <v>126837214</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8455,14 +8447,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>681315</v>
+        <v>681377</v>
       </c>
       <c r="R77" t="n">
-        <v>7086965</v>
+        <v>7087346</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8509,12 +8501,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8525,10 +8517,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126837214</v>
+        <v>126828689</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8536,34 +8528,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>681377</v>
+        <v>681562</v>
       </c>
       <c r="R78" t="n">
-        <v>7087346</v>
+        <v>7087373</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8593,9 +8597,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8610,12 +8624,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8626,10 +8640,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126840611</v>
+        <v>126837041</v>
       </c>
       <c r="B79" t="n">
-        <v>78773</v>
+        <v>79636</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8637,37 +8651,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>681406</v>
+        <v>681269</v>
       </c>
       <c r="R79" t="n">
-        <v>7087115</v>
+        <v>7087084</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8697,40 +8708,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8741,45 +8741,53 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126839934</v>
+        <v>126840216</v>
       </c>
       <c r="B80" t="n">
-        <v>79632</v>
+        <v>98447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>681223</v>
+        <v>681171</v>
       </c>
       <c r="R80" t="n">
-        <v>7087108</v>
+        <v>7087371</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8809,29 +8817,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8842,10 +8861,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126836433</v>
+        <v>126836211</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>91252</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8853,21 +8872,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8877,10 +8896,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>681377</v>
+        <v>681517</v>
       </c>
       <c r="R81" t="n">
-        <v>7087152</v>
+        <v>7086829</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8943,48 +8962,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126840136</v>
+        <v>126839934</v>
       </c>
       <c r="B82" t="n">
-        <v>91291</v>
+        <v>79636</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lamkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>681471</v>
+        <v>681223</v>
       </c>
       <c r="R82" t="n">
-        <v>7087265</v>
+        <v>7087108</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9014,40 +9030,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9058,10 +9063,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126836211</v>
+        <v>126841269</v>
       </c>
       <c r="B83" t="n">
-        <v>91248</v>
+        <v>78776</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9069,34 +9074,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>681517</v>
+        <v>680900</v>
       </c>
       <c r="R83" t="n">
-        <v>7086829</v>
+        <v>7087441</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9126,29 +9134,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9159,53 +9178,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126840216</v>
+        <v>126836433</v>
       </c>
       <c r="B84" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>681171</v>
+        <v>681377</v>
       </c>
       <c r="R84" t="n">
-        <v>7087371</v>
+        <v>7087152</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9235,40 +9246,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9279,32 +9279,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126841269</v>
+        <v>126840136</v>
       </c>
       <c r="B85" t="n">
-        <v>78772</v>
+        <v>91295</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9313,14 +9313,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Lamkullen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>680900</v>
+        <v>681471</v>
       </c>
       <c r="R85" t="n">
-        <v>7087441</v>
+        <v>7087265</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9394,10 +9394,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126838801</v>
+        <v>126837202</v>
       </c>
       <c r="B86" t="n">
-        <v>78773</v>
+        <v>80121</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9405,34 +9405,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>681359</v>
+        <v>680964</v>
       </c>
       <c r="R86" t="n">
-        <v>7087090</v>
+        <v>7087427</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9479,57 +9479,65 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126837202</v>
+        <v>126841337</v>
       </c>
       <c r="B87" t="n">
-        <v>80117</v>
+        <v>98364</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>680964</v>
+        <v>681071</v>
       </c>
       <c r="R87" t="n">
-        <v>7087427</v>
+        <v>7087437</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9559,29 +9567,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9595,7 +9614,7 @@
         <v>126837049</v>
       </c>
       <c r="B88" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9705,49 +9724,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126841337</v>
+        <v>126838801</v>
       </c>
       <c r="B89" t="n">
-        <v>98360</v>
+        <v>78777</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>681071</v>
+        <v>681359</v>
       </c>
       <c r="R89" t="n">
-        <v>7087437</v>
+        <v>7087090</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9777,54 +9792,39 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
         <v>126848802</v>
       </c>
       <c r="B90" t="n">
-        <v>80052</v>
+        <v>80056</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>126840233</v>
       </c>
       <c r="B91" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>126829744</v>
       </c>
       <c r="B92" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126836209</v>
+        <v>126837203</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681513</v>
+        <v>681075</v>
       </c>
       <c r="R2" t="n">
-        <v>7086833</v>
+        <v>7087404</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126837206</v>
+        <v>126836346</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>91491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680899</v>
+        <v>681265</v>
       </c>
       <c r="R3" t="n">
-        <v>7087435</v>
+        <v>7087123</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836346</v>
+        <v>126836209</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681265</v>
+        <v>681513</v>
       </c>
       <c r="R4" t="n">
-        <v>7087123</v>
+        <v>7086833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126837203</v>
+        <v>126837206</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681075</v>
+        <v>680899</v>
       </c>
       <c r="R5" t="n">
-        <v>7087404</v>
+        <v>7087435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1290,32 +1290,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836422</v>
+        <v>126837209</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681560</v>
+        <v>681166</v>
       </c>
       <c r="R8" t="n">
-        <v>7087320</v>
+        <v>7087366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,12 +1375,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1391,32 +1391,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126837209</v>
+        <v>126836422</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>681166</v>
+        <v>681560</v>
       </c>
       <c r="R9" t="n">
-        <v>7087366</v>
+        <v>7087320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,12 +1476,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836292</v>
+        <v>126840607</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,34 +1613,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>681520</v>
+        <v>681406</v>
       </c>
       <c r="R11" t="n">
-        <v>7086769</v>
+        <v>7087115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1670,29 +1673,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1703,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126840607</v>
+        <v>126837081</v>
       </c>
       <c r="B12" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,37 +1728,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>681406</v>
+        <v>681499</v>
       </c>
       <c r="R12" t="n">
-        <v>7087115</v>
+        <v>7087039</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,40 +1785,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126837081</v>
+        <v>126836292</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,34 +1930,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>681499</v>
+        <v>681520</v>
       </c>
       <c r="R14" t="n">
-        <v>7087039</v>
+        <v>7086769</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,12 +2004,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2236,45 +2236,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836219</v>
+        <v>126837065</v>
       </c>
       <c r="B17" t="n">
-        <v>91295</v>
+        <v>78777</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>681508</v>
+        <v>681401</v>
       </c>
       <c r="R17" t="n">
-        <v>7087463</v>
+        <v>7087113</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,12 +2321,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126838810</v>
+        <v>126836224</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>681251</v>
+        <v>681282</v>
       </c>
       <c r="R18" t="n">
-        <v>7086940</v>
+        <v>7087132</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,12 +2422,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836435</v>
+        <v>126836219</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>681329</v>
+        <v>681508</v>
       </c>
       <c r="R19" t="n">
-        <v>7087139</v>
+        <v>7087463</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126837065</v>
+        <v>126838810</v>
       </c>
       <c r="B20" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,34 +2550,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>681401</v>
+        <v>681251</v>
       </c>
       <c r="R20" t="n">
-        <v>7087113</v>
+        <v>7086940</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,12 +2624,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836224</v>
+        <v>126836435</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>681282</v>
+        <v>681329</v>
       </c>
       <c r="R21" t="n">
-        <v>7087132</v>
+        <v>7087139</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126837055</v>
+        <v>126836225</v>
       </c>
       <c r="B22" t="n">
-        <v>80025</v>
+        <v>58520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,34 +2752,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>208249</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>681459</v>
+        <v>681499</v>
       </c>
       <c r="R22" t="n">
-        <v>7087038</v>
+        <v>7087486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126836225</v>
+        <v>126837055</v>
       </c>
       <c r="B23" t="n">
-        <v>58520</v>
+        <v>80025</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,34 +2853,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208249</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>681499</v>
+        <v>681459</v>
       </c>
       <c r="R23" t="n">
-        <v>7087486</v>
+        <v>7087038</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,12 +2927,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126837217</v>
+        <v>126837042</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3055,34 +3055,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>681283</v>
+        <v>681238</v>
       </c>
       <c r="R25" t="n">
-        <v>7087132</v>
+        <v>7087139</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3129,12 +3129,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126837042</v>
+        <v>126837217</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3156,34 +3156,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>681238</v>
+        <v>681283</v>
       </c>
       <c r="R26" t="n">
-        <v>7087139</v>
+        <v>7087132</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,12 +3230,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3347,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836214</v>
+        <v>126839951</v>
       </c>
       <c r="B28" t="n">
-        <v>96700</v>
+        <v>57821</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>681496</v>
+        <v>681250</v>
       </c>
       <c r="R28" t="n">
-        <v>7087506</v>
+        <v>7087112</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,12 +3432,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3448,45 +3448,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126836297</v>
+        <v>126830094</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>681585</v>
+        <v>681091</v>
       </c>
       <c r="R29" t="n">
-        <v>7087270</v>
+        <v>7087426</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3516,29 +3528,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3549,10 +3572,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126839951</v>
+        <v>126836297</v>
       </c>
       <c r="B30" t="n">
-        <v>57821</v>
+        <v>78777</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3560,21 +3583,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3584,10 +3607,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>681250</v>
+        <v>681585</v>
       </c>
       <c r="R30" t="n">
-        <v>7087112</v>
+        <v>7087270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3634,12 +3657,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3650,57 +3673,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126830094</v>
+        <v>126836214</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>681091</v>
+        <v>681496</v>
       </c>
       <c r="R31" t="n">
-        <v>7087426</v>
+        <v>7087506</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,40 +3741,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3774,45 +3774,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126837072</v>
+        <v>126837194</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>681410</v>
+        <v>681159</v>
       </c>
       <c r="R32" t="n">
-        <v>7087105</v>
+        <v>7087381</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3875,45 +3875,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126837199</v>
+        <v>126837072</v>
       </c>
       <c r="B33" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680957</v>
+        <v>681410</v>
       </c>
       <c r="R33" t="n">
-        <v>7087424</v>
+        <v>7087105</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3960,12 +3960,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4178,32 +4178,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126837194</v>
+        <v>126837199</v>
       </c>
       <c r="B36" t="n">
-        <v>57821</v>
+        <v>80150</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>681159</v>
+        <v>680957</v>
       </c>
       <c r="R36" t="n">
-        <v>7087381</v>
+        <v>7087424</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126836232</v>
+        <v>126836221</v>
       </c>
       <c r="B37" t="n">
-        <v>56853</v>
+        <v>91295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4290,42 +4290,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>681509</v>
+        <v>681514</v>
       </c>
       <c r="R37" t="n">
-        <v>7087382</v>
+        <v>7087467</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4603,10 +4595,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836221</v>
+        <v>126836232</v>
       </c>
       <c r="B40" t="n">
-        <v>91295</v>
+        <v>56853</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4614,34 +4606,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>681514</v>
+        <v>681509</v>
       </c>
       <c r="R40" t="n">
-        <v>7087467</v>
+        <v>7087382</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126840180</v>
+        <v>126836426</v>
       </c>
       <c r="B42" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4830,37 +4830,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>681446</v>
+        <v>681490</v>
       </c>
       <c r="R42" t="n">
-        <v>7087459</v>
+        <v>7087351</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4890,40 +4887,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4934,10 +4920,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126836426</v>
+        <v>126840180</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,34 +4931,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>681490</v>
+        <v>681446</v>
       </c>
       <c r="R43" t="n">
-        <v>7087351</v>
+        <v>7087459</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5002,29 +4991,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5035,10 +5035,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836218</v>
+        <v>126837201</v>
       </c>
       <c r="B44" t="n">
-        <v>91295</v>
+        <v>97325</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,21 +5046,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5070,10 +5070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>681503</v>
+        <v>681070</v>
       </c>
       <c r="R44" t="n">
-        <v>7087483</v>
+        <v>7087424</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5120,12 +5120,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5348,10 +5348,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126837201</v>
+        <v>126836218</v>
       </c>
       <c r="B47" t="n">
-        <v>97325</v>
+        <v>91295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5359,21 +5359,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>681070</v>
+        <v>681503</v>
       </c>
       <c r="R47" t="n">
-        <v>7087424</v>
+        <v>7087483</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5433,12 +5433,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -6271,7 +6271,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126837080</v>
+        <v>126836421</v>
       </c>
       <c r="B56" t="n">
         <v>79018</v>
@@ -6302,14 +6302,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>681442</v>
+        <v>681572</v>
       </c>
       <c r="R56" t="n">
-        <v>7086944</v>
+        <v>7087305</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6356,12 +6356,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6372,45 +6372,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126836496</v>
+        <v>126837080</v>
       </c>
       <c r="B57" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>681155</v>
+        <v>681442</v>
       </c>
       <c r="R57" t="n">
-        <v>7087260</v>
+        <v>7086944</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6457,12 +6457,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6473,32 +6473,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126836421</v>
+        <v>126836496</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>681572</v>
+        <v>681155</v>
       </c>
       <c r="R58" t="n">
-        <v>7087305</v>
+        <v>7087260</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6776,10 +6776,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126836431</v>
+        <v>126836294</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6787,21 +6787,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>681443</v>
+        <v>681517</v>
       </c>
       <c r="R61" t="n">
-        <v>7087186</v>
+        <v>7086829</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6877,7 +6877,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126837230</v>
+        <v>126836431</v>
       </c>
       <c r="B62" t="n">
         <v>79018</v>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>680902</v>
+        <v>681443</v>
       </c>
       <c r="R62" t="n">
-        <v>7087430</v>
+        <v>7087186</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,12 +6962,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6978,10 +6978,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126837196</v>
+        <v>126837230</v>
       </c>
       <c r="B63" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6989,21 +6989,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>681047</v>
+        <v>680902</v>
       </c>
       <c r="R63" t="n">
-        <v>7087442</v>
+        <v>7087430</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7079,32 +7079,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836275</v>
+        <v>126837196</v>
       </c>
       <c r="B64" t="n">
-        <v>97325</v>
+        <v>57821</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>681493</v>
+        <v>681047</v>
       </c>
       <c r="R64" t="n">
-        <v>7087510</v>
+        <v>7087442</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,12 +7164,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7180,45 +7180,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126837067</v>
+        <v>126836275</v>
       </c>
       <c r="B65" t="n">
-        <v>78777</v>
+        <v>97325</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>681203</v>
+        <v>681493</v>
       </c>
       <c r="R65" t="n">
-        <v>7087139</v>
+        <v>7087510</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7265,12 +7265,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126836294</v>
+        <v>126837067</v>
       </c>
       <c r="B66" t="n">
         <v>78777</v>
@@ -7312,14 +7312,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>681517</v>
+        <v>681203</v>
       </c>
       <c r="R66" t="n">
-        <v>7086829</v>
+        <v>7087139</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7366,12 +7366,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7382,10 +7382,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126836274</v>
+        <v>126836220</v>
       </c>
       <c r="B67" t="n">
-        <v>97325</v>
+        <v>91295</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7393,21 +7393,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>681531</v>
+        <v>681510</v>
       </c>
       <c r="R67" t="n">
-        <v>7087468</v>
+        <v>7087465</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126836299</v>
+        <v>126837216</v>
       </c>
       <c r="B68" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>681313</v>
+        <v>681451</v>
       </c>
       <c r="R68" t="n">
         <v>7087136</v>
@@ -7568,12 +7568,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7584,10 +7584,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126837064</v>
+        <v>126837215</v>
       </c>
       <c r="B69" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7595,34 +7595,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>681464</v>
+        <v>681516</v>
       </c>
       <c r="R69" t="n">
-        <v>7087062</v>
+        <v>7087367</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7669,12 +7669,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7685,10 +7685,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126837216</v>
+        <v>126830801</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7696,34 +7696,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>681451</v>
+        <v>681063</v>
       </c>
       <c r="R70" t="n">
-        <v>7087136</v>
+        <v>7087438</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7753,9 +7753,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7770,12 +7780,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7786,10 +7796,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126837215</v>
+        <v>126836208</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7797,21 +7807,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7821,10 +7831,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>681516</v>
+        <v>681523</v>
       </c>
       <c r="R71" t="n">
-        <v>7087367</v>
+        <v>7086816</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7871,12 +7881,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7887,10 +7897,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126836220</v>
+        <v>126836274</v>
       </c>
       <c r="B72" t="n">
-        <v>91295</v>
+        <v>97325</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7898,21 +7908,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7922,10 +7932,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>681510</v>
+        <v>681531</v>
       </c>
       <c r="R72" t="n">
-        <v>7087465</v>
+        <v>7087468</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7988,10 +7998,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126830801</v>
+        <v>126836299</v>
       </c>
       <c r="B73" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7999,34 +8009,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>681063</v>
+        <v>681313</v>
       </c>
       <c r="R73" t="n">
-        <v>7087438</v>
+        <v>7087136</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8056,19 +8066,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8083,12 +8083,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8099,10 +8099,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126836208</v>
+        <v>126837064</v>
       </c>
       <c r="B74" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8110,34 +8110,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>681523</v>
+        <v>681464</v>
       </c>
       <c r="R74" t="n">
-        <v>7086816</v>
+        <v>7087062</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8184,12 +8184,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8200,10 +8200,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126840611</v>
+        <v>126828689</v>
       </c>
       <c r="B75" t="n">
-        <v>78777</v>
+        <v>57658</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8211,37 +8211,46 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>681406</v>
+        <v>681562</v>
       </c>
       <c r="R75" t="n">
-        <v>7087115</v>
+        <v>7087373</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8273,7 +8282,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8283,7 +8292,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8292,7 +8301,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8315,10 +8323,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126838812</v>
+        <v>126840611</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8326,34 +8334,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>681315</v>
+        <v>681406</v>
       </c>
       <c r="R76" t="n">
-        <v>7086965</v>
+        <v>7087115</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8383,29 +8394,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8416,10 +8438,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126837214</v>
+        <v>126837041</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8427,34 +8449,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>681377</v>
+        <v>681269</v>
       </c>
       <c r="R77" t="n">
-        <v>7087346</v>
+        <v>7087084</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8501,12 +8523,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8517,10 +8539,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126828689</v>
+        <v>126838812</v>
       </c>
       <c r="B78" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8528,46 +8550,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>681562</v>
+        <v>681315</v>
       </c>
       <c r="R78" t="n">
-        <v>7087373</v>
+        <v>7086965</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8597,19 +8607,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8624,12 +8624,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8640,10 +8640,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126837041</v>
+        <v>126837214</v>
       </c>
       <c r="B79" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8651,34 +8651,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>681269</v>
+        <v>681377</v>
       </c>
       <c r="R79" t="n">
-        <v>7087084</v>
+        <v>7087346</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8725,12 +8725,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8741,53 +8741,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126840216</v>
+        <v>126840136</v>
       </c>
       <c r="B80" t="n">
-        <v>98447</v>
+        <v>91295</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Lamkullen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>681171</v>
+        <v>681471</v>
       </c>
       <c r="R80" t="n">
-        <v>7087371</v>
+        <v>7087265</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8819,7 +8814,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8829,7 +8824,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9279,48 +9274,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126840136</v>
+        <v>126840216</v>
       </c>
       <c r="B85" t="n">
-        <v>91295</v>
+        <v>98447</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lamkullen, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>681471</v>
+        <v>681171</v>
       </c>
       <c r="R85" t="n">
-        <v>7087265</v>
+        <v>7087371</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9495,10 +9495,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126841337</v>
+        <v>126837049</v>
       </c>
       <c r="B87" t="n">
-        <v>98364</v>
+        <v>56853</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9506,38 +9506,46 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>681071</v>
+        <v>681376</v>
       </c>
       <c r="R87" t="n">
-        <v>7087437</v>
+        <v>7087119</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9567,40 +9575,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9611,10 +9608,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126837049</v>
+        <v>126841337</v>
       </c>
       <c r="B88" t="n">
-        <v>56853</v>
+        <v>98364</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9622,46 +9619,38 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>681376</v>
+        <v>681071</v>
       </c>
       <c r="R88" t="n">
-        <v>7087119</v>
+        <v>7087437</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9691,29 +9680,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9821,10 +9821,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126848802</v>
+        <v>126840233</v>
       </c>
       <c r="B90" t="n">
-        <v>80056</v>
+        <v>98483</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9832,40 +9832,49 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6457</v>
+        <v>223621</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>681455</v>
+        <v>681171</v>
       </c>
       <c r="R90" t="n">
-        <v>7087007</v>
+        <v>7087371</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9894,7 +9903,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9904,7 +9913,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9920,12 +9929,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9936,10 +9945,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126840233</v>
+        <v>126848802</v>
       </c>
       <c r="B91" t="n">
-        <v>98483</v>
+        <v>80056</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9947,49 +9956,40 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223621</v>
+        <v>6457</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>681171</v>
+        <v>681455</v>
       </c>
       <c r="R91" t="n">
-        <v>7087371</v>
+        <v>7087007</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10044,12 +10044,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -2741,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126836225</v>
+        <v>126837055</v>
       </c>
       <c r="B22" t="n">
-        <v>58520</v>
+        <v>80025</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,34 +2752,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208249</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>681499</v>
+        <v>681459</v>
       </c>
       <c r="R22" t="n">
-        <v>7087486</v>
+        <v>7087038</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126837055</v>
+        <v>126836225</v>
       </c>
       <c r="B23" t="n">
-        <v>80025</v>
+        <v>58520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,34 +2853,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>208249</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>681459</v>
+        <v>681499</v>
       </c>
       <c r="R23" t="n">
-        <v>7087038</v>
+        <v>7087486</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,12 +2927,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -4279,32 +4279,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126836221</v>
+        <v>126837208</v>
       </c>
       <c r="B37" t="n">
-        <v>91295</v>
+        <v>78776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>681514</v>
+        <v>681315</v>
       </c>
       <c r="R37" t="n">
-        <v>7087467</v>
+        <v>7087155</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4364,12 +4364,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4380,10 +4380,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126837208</v>
+        <v>126837200</v>
       </c>
       <c r="B38" t="n">
-        <v>78776</v>
+        <v>57658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4391,34 +4391,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>681315</v>
+        <v>681264</v>
       </c>
       <c r="R38" t="n">
-        <v>7087155</v>
+        <v>7087324</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,6 +4459,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4481,32 +4494,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126837200</v>
+        <v>126836232</v>
       </c>
       <c r="B39" t="n">
-        <v>57658</v>
+        <v>56853</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4514,7 +4527,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4524,10 +4537,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>681264</v>
+        <v>681509</v>
       </c>
       <c r="R39" t="n">
-        <v>7087324</v>
+        <v>7087382</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4562,11 +4575,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4579,12 +4587,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4595,10 +4603,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836232</v>
+        <v>126836221</v>
       </c>
       <c r="B40" t="n">
-        <v>56853</v>
+        <v>91295</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4606,42 +4614,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>681509</v>
+        <v>681514</v>
       </c>
       <c r="R40" t="n">
-        <v>7087382</v>
+        <v>7087467</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,59 +4704,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126836349</v>
+        <v>126836426</v>
       </c>
       <c r="B41" t="n">
-        <v>98481</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>681163</v>
+        <v>681490</v>
       </c>
       <c r="R41" t="n">
-        <v>7087254</v>
+        <v>7087351</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4819,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126836426</v>
+        <v>126840180</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4830,34 +4816,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>681490</v>
+        <v>681446</v>
       </c>
       <c r="R42" t="n">
-        <v>7087351</v>
+        <v>7087459</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,29 +4876,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4920,48 +4920,59 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126840180</v>
+        <v>126836349</v>
       </c>
       <c r="B43" t="n">
-        <v>80121</v>
+        <v>98481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>681446</v>
+        <v>681163</v>
       </c>
       <c r="R43" t="n">
-        <v>7087459</v>
+        <v>7087254</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4991,40 +5002,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -6574,32 +6574,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126837211</v>
+        <v>126836431</v>
       </c>
       <c r="B59" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>681207</v>
+        <v>681443</v>
       </c>
       <c r="R59" t="n">
-        <v>7087379</v>
+        <v>7087186</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6659,12 +6659,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6675,32 +6675,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126837210</v>
+        <v>126837230</v>
       </c>
       <c r="B60" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>681199</v>
+        <v>680902</v>
       </c>
       <c r="R60" t="n">
-        <v>7087367</v>
+        <v>7087430</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6776,10 +6776,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126836294</v>
+        <v>126837196</v>
       </c>
       <c r="B61" t="n">
-        <v>78777</v>
+        <v>57821</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6787,21 +6787,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>681517</v>
+        <v>681047</v>
       </c>
       <c r="R61" t="n">
-        <v>7086829</v>
+        <v>7087442</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6861,12 +6861,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6877,32 +6877,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126836431</v>
+        <v>126837211</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>681443</v>
+        <v>681207</v>
       </c>
       <c r="R62" t="n">
-        <v>7087186</v>
+        <v>7087379</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,12 +6962,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6978,32 +6978,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126837230</v>
+        <v>126837210</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>680902</v>
+        <v>681199</v>
       </c>
       <c r="R63" t="n">
-        <v>7087430</v>
+        <v>7087367</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7079,10 +7079,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126837196</v>
+        <v>126837067</v>
       </c>
       <c r="B64" t="n">
-        <v>57821</v>
+        <v>78777</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7090,34 +7090,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>681047</v>
+        <v>681203</v>
       </c>
       <c r="R64" t="n">
-        <v>7087442</v>
+        <v>7087139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,12 +7164,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7180,32 +7180,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126836275</v>
+        <v>126836294</v>
       </c>
       <c r="B65" t="n">
-        <v>97325</v>
+        <v>78777</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>681493</v>
+        <v>681517</v>
       </c>
       <c r="R65" t="n">
-        <v>7087510</v>
+        <v>7086829</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7281,45 +7281,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126837067</v>
+        <v>126836275</v>
       </c>
       <c r="B66" t="n">
-        <v>78777</v>
+        <v>97325</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>681203</v>
+        <v>681493</v>
       </c>
       <c r="R66" t="n">
-        <v>7087139</v>
+        <v>7087510</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7366,12 +7366,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7382,32 +7382,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126836220</v>
+        <v>126837215</v>
       </c>
       <c r="B67" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>681510</v>
+        <v>681516</v>
       </c>
       <c r="R67" t="n">
-        <v>7087465</v>
+        <v>7087367</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7467,12 +7467,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7483,10 +7483,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126837216</v>
+        <v>126836208</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>681451</v>
+        <v>681523</v>
       </c>
       <c r="R68" t="n">
-        <v>7087136</v>
+        <v>7086816</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7568,12 +7568,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7584,32 +7584,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126837215</v>
+        <v>126836274</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>97325</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>681516</v>
+        <v>681531</v>
       </c>
       <c r="R69" t="n">
-        <v>7087367</v>
+        <v>7087468</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7669,12 +7669,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7685,45 +7685,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126830801</v>
+        <v>126836220</v>
       </c>
       <c r="B70" t="n">
-        <v>78776</v>
+        <v>91295</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>681063</v>
+        <v>681510</v>
       </c>
       <c r="R70" t="n">
-        <v>7087438</v>
+        <v>7087465</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7753,19 +7753,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7780,12 +7770,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7796,10 +7786,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126836208</v>
+        <v>126837216</v>
       </c>
       <c r="B71" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7807,21 +7797,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7831,10 +7821,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>681523</v>
+        <v>681451</v>
       </c>
       <c r="R71" t="n">
-        <v>7086816</v>
+        <v>7087136</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7881,12 +7871,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7897,45 +7887,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126836274</v>
+        <v>126830801</v>
       </c>
       <c r="B72" t="n">
-        <v>97325</v>
+        <v>78776</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>681531</v>
+        <v>681063</v>
       </c>
       <c r="R72" t="n">
-        <v>7087468</v>
+        <v>7087438</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7965,9 +7955,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7982,12 +7982,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -9394,45 +9394,57 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126837202</v>
+        <v>126837049</v>
       </c>
       <c r="B86" t="n">
-        <v>80121</v>
+        <v>56853</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>680964</v>
+        <v>681376</v>
       </c>
       <c r="R86" t="n">
-        <v>7087427</v>
+        <v>7087119</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9479,12 +9491,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9495,57 +9507,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126837049</v>
+        <v>126838801</v>
       </c>
       <c r="B87" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>681376</v>
+        <v>681359</v>
       </c>
       <c r="R87" t="n">
-        <v>7087119</v>
+        <v>7087090</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9592,65 +9592,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126841337</v>
+        <v>126837202</v>
       </c>
       <c r="B88" t="n">
-        <v>98364</v>
+        <v>80121</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>681071</v>
+        <v>680964</v>
       </c>
       <c r="R88" t="n">
-        <v>7087437</v>
+        <v>7087427</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9680,40 +9672,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9724,45 +9705,49 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126838801</v>
+        <v>126841337</v>
       </c>
       <c r="B89" t="n">
-        <v>78777</v>
+        <v>98364</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>681359</v>
+        <v>681071</v>
       </c>
       <c r="R89" t="n">
-        <v>7087090</v>
+        <v>7087437</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9792,32 +9777,47 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -2236,45 +2236,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126837065</v>
+        <v>126836219</v>
       </c>
       <c r="B17" t="n">
-        <v>78777</v>
+        <v>91295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>681401</v>
+        <v>681508</v>
       </c>
       <c r="R17" t="n">
-        <v>7087113</v>
+        <v>7087463</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,12 +2321,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836224</v>
+        <v>126838810</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>681282</v>
+        <v>681251</v>
       </c>
       <c r="R18" t="n">
-        <v>7087132</v>
+        <v>7086940</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,12 +2422,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2438,32 +2438,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836219</v>
+        <v>126836435</v>
       </c>
       <c r="B19" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>681508</v>
+        <v>681329</v>
       </c>
       <c r="R19" t="n">
-        <v>7087463</v>
+        <v>7087139</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126838810</v>
+        <v>126837065</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,34 +2550,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>681251</v>
+        <v>681401</v>
       </c>
       <c r="R20" t="n">
-        <v>7086940</v>
+        <v>7087113</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,12 +2624,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836435</v>
+        <v>126836224</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>681329</v>
+        <v>681282</v>
       </c>
       <c r="R21" t="n">
-        <v>7087139</v>
+        <v>7087132</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3448,57 +3448,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126830094</v>
+        <v>126836214</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>681091</v>
+        <v>681496</v>
       </c>
       <c r="R29" t="n">
-        <v>7087426</v>
+        <v>7087506</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3528,40 +3516,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3673,45 +3650,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126836214</v>
+        <v>126830094</v>
       </c>
       <c r="B31" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>681496</v>
+        <v>681091</v>
       </c>
       <c r="R31" t="n">
-        <v>7087506</v>
+        <v>7087426</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3741,29 +3730,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3774,10 +3774,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126837194</v>
+        <v>126836425</v>
       </c>
       <c r="B32" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3785,21 +3785,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>681159</v>
+        <v>681499</v>
       </c>
       <c r="R32" t="n">
         <v>7087381</v>
@@ -3859,12 +3859,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3875,45 +3875,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126837072</v>
+        <v>126836424</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>681410</v>
+        <v>681515</v>
       </c>
       <c r="R33" t="n">
-        <v>7087105</v>
+        <v>7087397</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3960,12 +3960,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3976,45 +3976,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836425</v>
+        <v>126837072</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>681499</v>
+        <v>681410</v>
       </c>
       <c r="R34" t="n">
-        <v>7087381</v>
+        <v>7087105</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,12 +4061,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4077,32 +4077,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126836424</v>
+        <v>126837199</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>681515</v>
+        <v>680957</v>
       </c>
       <c r="R35" t="n">
-        <v>7087397</v>
+        <v>7087424</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4162,12 +4162,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4178,32 +4178,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126837199</v>
+        <v>126837194</v>
       </c>
       <c r="B36" t="n">
-        <v>80150</v>
+        <v>57821</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>680957</v>
+        <v>681159</v>
       </c>
       <c r="R36" t="n">
-        <v>7087424</v>
+        <v>7087381</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126837208</v>
+        <v>126836221</v>
       </c>
       <c r="B37" t="n">
-        <v>78776</v>
+        <v>91295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>681315</v>
+        <v>681514</v>
       </c>
       <c r="R37" t="n">
-        <v>7087155</v>
+        <v>7087467</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4364,12 +4364,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4380,10 +4380,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126837200</v>
+        <v>126837208</v>
       </c>
       <c r="B38" t="n">
-        <v>57658</v>
+        <v>78776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4391,42 +4391,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>681264</v>
+        <v>681315</v>
       </c>
       <c r="R38" t="n">
-        <v>7087324</v>
+        <v>7087155</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,11 +4451,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4494,32 +4481,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836232</v>
+        <v>126837200</v>
       </c>
       <c r="B39" t="n">
-        <v>56853</v>
+        <v>57658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4527,7 +4514,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4537,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>681509</v>
+        <v>681264</v>
       </c>
       <c r="R39" t="n">
-        <v>7087382</v>
+        <v>7087324</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4575,6 +4562,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4587,12 +4579,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4603,10 +4595,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836221</v>
+        <v>126836232</v>
       </c>
       <c r="B40" t="n">
-        <v>91295</v>
+        <v>56853</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4614,34 +4606,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>681514</v>
+        <v>681509</v>
       </c>
       <c r="R40" t="n">
-        <v>7087467</v>
+        <v>7087382</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5035,45 +5035,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126837201</v>
+        <v>126830813</v>
       </c>
       <c r="B44" t="n">
-        <v>97325</v>
+        <v>79636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>681070</v>
+        <v>680904</v>
       </c>
       <c r="R44" t="n">
-        <v>7087424</v>
+        <v>7087434</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,9 +5103,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5120,12 +5130,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5136,10 +5146,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126830813</v>
+        <v>126837207</v>
       </c>
       <c r="B45" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5147,34 +5157,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680904</v>
+        <v>681407</v>
       </c>
       <c r="R45" t="n">
-        <v>7087434</v>
+        <v>7087119</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5204,19 +5214,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5231,12 +5231,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5247,32 +5247,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126837207</v>
+        <v>126836218</v>
       </c>
       <c r="B46" t="n">
-        <v>78776</v>
+        <v>91295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>681407</v>
+        <v>681503</v>
       </c>
       <c r="R46" t="n">
-        <v>7087119</v>
+        <v>7087483</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5332,12 +5332,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5348,10 +5348,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836218</v>
+        <v>126837201</v>
       </c>
       <c r="B47" t="n">
-        <v>91295</v>
+        <v>97325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5359,21 +5359,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>681503</v>
+        <v>681070</v>
       </c>
       <c r="R47" t="n">
-        <v>7087483</v>
+        <v>7087424</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5433,12 +5433,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -9394,57 +9394,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126837049</v>
+        <v>126837202</v>
       </c>
       <c r="B86" t="n">
-        <v>56853</v>
+        <v>80121</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>681376</v>
+        <v>680964</v>
       </c>
       <c r="R86" t="n">
-        <v>7087119</v>
+        <v>7087427</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9491,12 +9479,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9507,45 +9495,57 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126838801</v>
+        <v>126837049</v>
       </c>
       <c r="B87" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>681359</v>
+        <v>681376</v>
       </c>
       <c r="R87" t="n">
-        <v>7087090</v>
+        <v>7087119</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9592,57 +9592,65 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126837202</v>
+        <v>126841337</v>
       </c>
       <c r="B88" t="n">
-        <v>80121</v>
+        <v>98364</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>680964</v>
+        <v>681071</v>
       </c>
       <c r="R88" t="n">
-        <v>7087427</v>
+        <v>7087437</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9672,29 +9680,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9705,49 +9724,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126841337</v>
+        <v>126838801</v>
       </c>
       <c r="B89" t="n">
-        <v>98364</v>
+        <v>78777</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>681071</v>
+        <v>681359</v>
       </c>
       <c r="R89" t="n">
-        <v>7087437</v>
+        <v>7087090</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9777,47 +9792,32 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126837203</v>
+        <v>126836346</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>91491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681075</v>
+        <v>681265</v>
       </c>
       <c r="R2" t="n">
-        <v>7087404</v>
+        <v>7087123</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836346</v>
+        <v>126837206</v>
       </c>
       <c r="B3" t="n">
-        <v>91491</v>
+        <v>78776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681265</v>
+        <v>680899</v>
       </c>
       <c r="R3" t="n">
-        <v>7087123</v>
+        <v>7087435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836209</v>
+        <v>126837203</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681513</v>
+        <v>681075</v>
       </c>
       <c r="R4" t="n">
-        <v>7086833</v>
+        <v>7087404</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126837206</v>
+        <v>126836209</v>
       </c>
       <c r="B5" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680899</v>
+        <v>681513</v>
       </c>
       <c r="R5" t="n">
-        <v>7087435</v>
+        <v>7086833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1082,7 +1082,7 @@
         <v>126836318</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,45 +1189,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836434</v>
+        <v>126836231</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681368</v>
+        <v>681110</v>
       </c>
       <c r="R7" t="n">
-        <v>7087145</v>
+        <v>7087306</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,32 +1299,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126837209</v>
+        <v>126836434</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681166</v>
+        <v>681368</v>
       </c>
       <c r="R8" t="n">
-        <v>7087366</v>
+        <v>7087145</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,12 +1384,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1492,54 +1501,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836231</v>
+        <v>126837209</v>
       </c>
       <c r="B10" t="n">
-        <v>56853</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>681110</v>
+        <v>681166</v>
       </c>
       <c r="R10" t="n">
-        <v>7087306</v>
+        <v>7087366</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1586,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126840607</v>
+        <v>126837081</v>
       </c>
       <c r="B11" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,37 +1613,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>681406</v>
+        <v>681499</v>
       </c>
       <c r="R11" t="n">
-        <v>7087115</v>
+        <v>7087039</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,40 +1670,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1717,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126837081</v>
+        <v>126836292</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1728,34 +1714,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>681499</v>
+        <v>681520</v>
       </c>
       <c r="R12" t="n">
-        <v>7087039</v>
+        <v>7086769</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,12 +1788,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1919,10 +1905,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836292</v>
+        <v>126840607</v>
       </c>
       <c r="B14" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,34 +1916,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>681520</v>
+        <v>681406</v>
       </c>
       <c r="R14" t="n">
-        <v>7086769</v>
+        <v>7087115</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,29 +1976,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126840170</v>
+        <v>126840005</v>
       </c>
       <c r="B15" t="n">
-        <v>80150</v>
+        <v>8439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,37 +2031,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>681446</v>
+        <v>681380</v>
       </c>
       <c r="R15" t="n">
-        <v>7087459</v>
+        <v>7087013</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,40 +2088,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2135,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126840005</v>
+        <v>126840170</v>
       </c>
       <c r="B16" t="n">
-        <v>8439</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,34 +2132,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>681380</v>
+        <v>681446</v>
       </c>
       <c r="R16" t="n">
-        <v>7087013</v>
+        <v>7087459</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,29 +2192,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2236,32 +2236,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836219</v>
+        <v>126836224</v>
       </c>
       <c r="B17" t="n">
-        <v>91295</v>
+        <v>79607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>681508</v>
+        <v>681282</v>
       </c>
       <c r="R17" t="n">
-        <v>7087463</v>
+        <v>7087132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126838810</v>
+        <v>126837065</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>681251</v>
+        <v>681401</v>
       </c>
       <c r="R18" t="n">
-        <v>7086940</v>
+        <v>7087113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,12 +2422,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2539,45 +2539,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126837065</v>
+        <v>126836219</v>
       </c>
       <c r="B20" t="n">
-        <v>78777</v>
+        <v>91295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>681401</v>
+        <v>681508</v>
       </c>
       <c r="R20" t="n">
-        <v>7087113</v>
+        <v>7087463</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,12 +2624,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2640,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836224</v>
+        <v>126838810</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,34 +2651,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>681282</v>
+        <v>681251</v>
       </c>
       <c r="R21" t="n">
-        <v>7087132</v>
+        <v>7086940</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,12 +2725,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2741,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126837055</v>
+        <v>126836225</v>
       </c>
       <c r="B22" t="n">
-        <v>80025</v>
+        <v>58520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,34 +2752,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>208249</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>681459</v>
+        <v>681499</v>
       </c>
       <c r="R22" t="n">
-        <v>7087038</v>
+        <v>7087486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126836225</v>
+        <v>126837055</v>
       </c>
       <c r="B23" t="n">
-        <v>58520</v>
+        <v>80025</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,34 +2853,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208249</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>681499</v>
+        <v>681459</v>
       </c>
       <c r="R23" t="n">
-        <v>7087486</v>
+        <v>7087038</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,12 +2927,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2943,10 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126836432</v>
+        <v>126837042</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,34 +2954,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>681386</v>
+        <v>681238</v>
       </c>
       <c r="R24" t="n">
-        <v>7087146</v>
+        <v>7087139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,12 +3028,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126837042</v>
+        <v>126837217</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3055,34 +3055,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>681238</v>
+        <v>681283</v>
       </c>
       <c r="R25" t="n">
-        <v>7087139</v>
+        <v>7087132</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3129,12 +3129,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3145,7 +3145,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126837217</v>
+        <v>126836432</v>
       </c>
       <c r="B26" t="n">
         <v>79018</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>681283</v>
+        <v>681386</v>
       </c>
       <c r="R26" t="n">
-        <v>7087132</v>
+        <v>7087146</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,12 +3230,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3246,10 +3246,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836427</v>
+        <v>126836214</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>96700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>681540</v>
+        <v>681496</v>
       </c>
       <c r="R27" t="n">
-        <v>7087272</v>
+        <v>7087506</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126839951</v>
+        <v>126836427</v>
       </c>
       <c r="B28" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>681250</v>
+        <v>681540</v>
       </c>
       <c r="R28" t="n">
-        <v>7087112</v>
+        <v>7087272</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,12 +3432,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126836214</v>
+        <v>126839951</v>
       </c>
       <c r="B29" t="n">
-        <v>96700</v>
+        <v>57821</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,21 +3459,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>681496</v>
+        <v>681250</v>
       </c>
       <c r="R29" t="n">
-        <v>7087506</v>
+        <v>7087112</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,12 +3533,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3549,45 +3549,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126836297</v>
+        <v>126830094</v>
       </c>
       <c r="B30" t="n">
-        <v>78777</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>681585</v>
+        <v>681091</v>
       </c>
       <c r="R30" t="n">
-        <v>7087270</v>
+        <v>7087426</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3617,29 +3629,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3650,57 +3673,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126830094</v>
+        <v>126836297</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>681091</v>
+        <v>681585</v>
       </c>
       <c r="R31" t="n">
-        <v>7087426</v>
+        <v>7087270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,40 +3741,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3774,45 +3774,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836425</v>
+        <v>126837072</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>681499</v>
+        <v>681410</v>
       </c>
       <c r="R32" t="n">
-        <v>7087381</v>
+        <v>7087105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3976,45 +3976,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126837072</v>
+        <v>126836425</v>
       </c>
       <c r="B34" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>681410</v>
+        <v>681499</v>
       </c>
       <c r="R34" t="n">
-        <v>7087105</v>
+        <v>7087381</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,12 +4061,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4279,45 +4279,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126836221</v>
+        <v>126837200</v>
       </c>
       <c r="B37" t="n">
-        <v>91295</v>
+        <v>57658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>681514</v>
+        <v>681264</v>
       </c>
       <c r="R37" t="n">
-        <v>7087467</v>
+        <v>7087324</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4352,6 +4360,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4364,12 +4377,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4481,53 +4494,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126837200</v>
+        <v>126836221</v>
       </c>
       <c r="B39" t="n">
-        <v>57658</v>
+        <v>91295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>681264</v>
+        <v>681514</v>
       </c>
       <c r="R39" t="n">
-        <v>7087324</v>
+        <v>7087467</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4562,11 +4567,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4579,12 +4579,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4704,45 +4704,59 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126836426</v>
+        <v>126836349</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>98482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>681490</v>
+        <v>681163</v>
       </c>
       <c r="R41" t="n">
-        <v>7087351</v>
+        <v>7087254</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,59 +4934,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126836349</v>
+        <v>126836426</v>
       </c>
       <c r="B43" t="n">
-        <v>98481</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>681163</v>
+        <v>681490</v>
       </c>
       <c r="R43" t="n">
-        <v>7087254</v>
+        <v>7087351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5035,45 +5035,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126830813</v>
+        <v>126836218</v>
       </c>
       <c r="B44" t="n">
-        <v>79636</v>
+        <v>91295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680904</v>
+        <v>681503</v>
       </c>
       <c r="R44" t="n">
-        <v>7087434</v>
+        <v>7087483</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,19 +5103,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5130,12 +5120,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5146,10 +5136,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126837207</v>
+        <v>126830813</v>
       </c>
       <c r="B45" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5157,34 +5147,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>681407</v>
+        <v>680904</v>
       </c>
       <c r="R45" t="n">
-        <v>7087119</v>
+        <v>7087434</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5214,9 +5204,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5231,12 +5231,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5247,32 +5247,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126836218</v>
+        <v>126837207</v>
       </c>
       <c r="B46" t="n">
-        <v>91295</v>
+        <v>78776</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>681503</v>
+        <v>681407</v>
       </c>
       <c r="R46" t="n">
-        <v>7087483</v>
+        <v>7087119</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5332,12 +5332,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5449,10 +5449,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836534</v>
+        <v>126837051</v>
       </c>
       <c r="B48" t="n">
-        <v>78685</v>
+        <v>57821</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5460,34 +5460,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>681563</v>
+        <v>681251</v>
       </c>
       <c r="R48" t="n">
-        <v>7087315</v>
+        <v>7087107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,12 +5534,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126837040</v>
+        <v>126836534</v>
       </c>
       <c r="B49" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5561,34 +5561,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>681402</v>
+        <v>681563</v>
       </c>
       <c r="R49" t="n">
-        <v>7087113</v>
+        <v>7087315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5635,12 +5635,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5651,10 +5651,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126837051</v>
+        <v>126837040</v>
       </c>
       <c r="B50" t="n">
-        <v>57821</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5662,21 +5662,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>681251</v>
+        <v>681402</v>
       </c>
       <c r="R50" t="n">
-        <v>7087107</v>
+        <v>7087113</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5752,48 +5752,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126840200</v>
+        <v>126836423</v>
       </c>
       <c r="B51" t="n">
-        <v>91491</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>681091</v>
+        <v>681555</v>
       </c>
       <c r="R51" t="n">
-        <v>7087431</v>
+        <v>7087326</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5823,40 +5820,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5867,10 +5853,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836423</v>
+        <v>126837204</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5878,21 +5864,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5902,10 +5888,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>681555</v>
+        <v>681057</v>
       </c>
       <c r="R52" t="n">
-        <v>7087326</v>
+        <v>7087434</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5952,12 +5938,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5968,45 +5954,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126837204</v>
+        <v>126840200</v>
       </c>
       <c r="B53" t="n">
-        <v>80121</v>
+        <v>91491</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>681057</v>
+        <v>681091</v>
       </c>
       <c r="R53" t="n">
-        <v>7087434</v>
+        <v>7087431</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6036,29 +6025,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6170,10 +6170,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126837237</v>
+        <v>126836496</v>
       </c>
       <c r="B55" t="n">
-        <v>92620</v>
+        <v>98365</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>681451</v>
+        <v>681155</v>
       </c>
       <c r="R55" t="n">
-        <v>7087145</v>
+        <v>7087260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6255,12 +6255,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6473,10 +6473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126836496</v>
+        <v>126837237</v>
       </c>
       <c r="B58" t="n">
-        <v>98364</v>
+        <v>92620</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>681155</v>
+        <v>681451</v>
       </c>
       <c r="R58" t="n">
-        <v>7087260</v>
+        <v>7087145</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6558,12 +6558,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6776,32 +6776,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126837196</v>
+        <v>126837210</v>
       </c>
       <c r="B61" t="n">
-        <v>57821</v>
+        <v>98448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>681047</v>
+        <v>681199</v>
       </c>
       <c r="R61" t="n">
-        <v>7087442</v>
+        <v>7087367</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6880,7 +6880,7 @@
         <v>126837211</v>
       </c>
       <c r="B62" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6978,32 +6978,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126837210</v>
+        <v>126836275</v>
       </c>
       <c r="B63" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>681199</v>
+        <v>681493</v>
       </c>
       <c r="R63" t="n">
-        <v>7087367</v>
+        <v>7087510</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7063,12 +7063,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7079,7 +7079,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126837067</v>
+        <v>126836294</v>
       </c>
       <c r="B64" t="n">
         <v>78777</v>
@@ -7110,14 +7110,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>681203</v>
+        <v>681517</v>
       </c>
       <c r="R64" t="n">
-        <v>7087139</v>
+        <v>7086829</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,12 +7164,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7180,10 +7180,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126836294</v>
+        <v>126837196</v>
       </c>
       <c r="B65" t="n">
-        <v>78777</v>
+        <v>57821</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>681517</v>
+        <v>681047</v>
       </c>
       <c r="R65" t="n">
-        <v>7086829</v>
+        <v>7087442</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7265,12 +7265,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7281,45 +7281,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126836275</v>
+        <v>126837067</v>
       </c>
       <c r="B66" t="n">
-        <v>97325</v>
+        <v>78777</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>681493</v>
+        <v>681203</v>
       </c>
       <c r="R66" t="n">
-        <v>7087510</v>
+        <v>7087139</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7366,12 +7366,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7483,32 +7483,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126836208</v>
+        <v>126836220</v>
       </c>
       <c r="B68" t="n">
-        <v>79636</v>
+        <v>91295</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>681523</v>
+        <v>681510</v>
       </c>
       <c r="R68" t="n">
-        <v>7086816</v>
+        <v>7087465</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,32 +7584,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126836274</v>
+        <v>126837216</v>
       </c>
       <c r="B69" t="n">
-        <v>97325</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>681531</v>
+        <v>681451</v>
       </c>
       <c r="R69" t="n">
-        <v>7087468</v>
+        <v>7087136</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7669,12 +7669,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7685,45 +7685,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126836220</v>
+        <v>126830801</v>
       </c>
       <c r="B70" t="n">
-        <v>91295</v>
+        <v>78776</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>681510</v>
+        <v>681063</v>
       </c>
       <c r="R70" t="n">
-        <v>7087465</v>
+        <v>7087438</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7753,9 +7753,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7770,12 +7780,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7786,10 +7796,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126837216</v>
+        <v>126836208</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7797,21 +7807,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7821,10 +7831,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>681451</v>
+        <v>681523</v>
       </c>
       <c r="R71" t="n">
-        <v>7087136</v>
+        <v>7086816</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7871,12 +7881,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7887,45 +7897,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126830801</v>
+        <v>126836274</v>
       </c>
       <c r="B72" t="n">
-        <v>78776</v>
+        <v>97325</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>681063</v>
+        <v>681531</v>
       </c>
       <c r="R72" t="n">
-        <v>7087438</v>
+        <v>7087468</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7955,19 +7965,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7982,12 +7982,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8200,10 +8200,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126828689</v>
+        <v>126840611</v>
       </c>
       <c r="B75" t="n">
-        <v>57658</v>
+        <v>78777</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8211,46 +8211,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>681562</v>
+        <v>681406</v>
       </c>
       <c r="R75" t="n">
-        <v>7087373</v>
+        <v>7087115</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8282,7 +8273,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8292,7 +8283,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8301,6 +8292,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8323,10 +8315,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126840611</v>
+        <v>126837041</v>
       </c>
       <c r="B76" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8334,37 +8326,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>681406</v>
+        <v>681269</v>
       </c>
       <c r="R76" t="n">
-        <v>7087115</v>
+        <v>7087084</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8394,40 +8383,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8438,10 +8416,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126837041</v>
+        <v>126828689</v>
       </c>
       <c r="B77" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8449,34 +8427,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>681269</v>
+        <v>681562</v>
       </c>
       <c r="R77" t="n">
-        <v>7087084</v>
+        <v>7087373</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8506,9 +8496,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8523,12 +8523,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8741,48 +8741,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126840136</v>
+        <v>126839934</v>
       </c>
       <c r="B80" t="n">
-        <v>91295</v>
+        <v>79636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lamkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>681471</v>
+        <v>681223</v>
       </c>
       <c r="R80" t="n">
-        <v>7087265</v>
+        <v>7087108</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8812,40 +8809,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8856,10 +8842,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126836211</v>
+        <v>126841269</v>
       </c>
       <c r="B81" t="n">
-        <v>91252</v>
+        <v>78776</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8867,34 +8853,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>681517</v>
+        <v>680900</v>
       </c>
       <c r="R81" t="n">
-        <v>7086829</v>
+        <v>7087441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8924,29 +8913,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8957,10 +8957,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126839934</v>
+        <v>126836211</v>
       </c>
       <c r="B82" t="n">
-        <v>79636</v>
+        <v>91252</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8968,21 +8968,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>681223</v>
+        <v>681517</v>
       </c>
       <c r="R82" t="n">
-        <v>7087108</v>
+        <v>7086829</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9042,12 +9042,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9058,32 +9058,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126841269</v>
+        <v>126840136</v>
       </c>
       <c r="B83" t="n">
-        <v>78776</v>
+        <v>91295</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9092,14 +9092,14 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Lamkullen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>680900</v>
+        <v>681471</v>
       </c>
       <c r="R83" t="n">
-        <v>7087441</v>
+        <v>7087265</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9277,7 +9277,7 @@
         <v>126840216</v>
       </c>
       <c r="B85" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>126841337</v>
       </c>
       <c r="B88" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9821,10 +9821,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126840233</v>
+        <v>126848802</v>
       </c>
       <c r="B90" t="n">
-        <v>98483</v>
+        <v>80056</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9832,49 +9832,40 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>223621</v>
+        <v>6457</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>681171</v>
+        <v>681455</v>
       </c>
       <c r="R90" t="n">
-        <v>7087371</v>
+        <v>7087007</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9903,7 +9894,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9913,7 +9904,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9929,12 +9920,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9945,10 +9936,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126848802</v>
+        <v>126840233</v>
       </c>
       <c r="B91" t="n">
-        <v>80056</v>
+        <v>98484</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9956,40 +9947,49 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6457</v>
+        <v>223621</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>681455</v>
+        <v>681171</v>
       </c>
       <c r="R91" t="n">
-        <v>7087007</v>
+        <v>7087371</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10044,12 +10044,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10063,7 +10063,7 @@
         <v>126829744</v>
       </c>
       <c r="B92" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -9821,10 +9821,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126848802</v>
+        <v>126840233</v>
       </c>
       <c r="B90" t="n">
-        <v>80056</v>
+        <v>98484</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9832,40 +9832,49 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6457</v>
+        <v>223621</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>681455</v>
+        <v>681171</v>
       </c>
       <c r="R90" t="n">
-        <v>7087007</v>
+        <v>7087371</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9894,7 +9903,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9904,7 +9913,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9920,12 +9929,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9936,10 +9945,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126840233</v>
+        <v>126848802</v>
       </c>
       <c r="B91" t="n">
-        <v>98484</v>
+        <v>80056</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9947,49 +9956,40 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223621</v>
+        <v>6457</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>681171</v>
+        <v>681455</v>
       </c>
       <c r="R91" t="n">
-        <v>7087371</v>
+        <v>7087007</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10044,12 +10044,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10183,6 +10183,200 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129166277</v>
+      </c>
+      <c r="B93" t="n">
+        <v>98573</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Bredträsk, Ång</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>681422</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7087327</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Via Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129165953</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Bredträsk, Ång</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>681168</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7087371</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Via Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10188,7 +10188,7 @@
         <v>129166277</v>
       </c>
       <c r="B93" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>129165953</v>
       </c>
       <c r="B94" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10188,7 +10188,7 @@
         <v>129166277</v>
       </c>
       <c r="B93" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>129165953</v>
       </c>
       <c r="B94" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10188,7 +10188,7 @@
         <v>129166277</v>
       </c>
       <c r="B93" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>129165953</v>
       </c>
       <c r="B94" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10188,7 +10188,7 @@
         <v>129166277</v>
       </c>
       <c r="B93" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>129165953</v>
       </c>
       <c r="B94" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10183,200 +10183,6 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>129166277</v>
-      </c>
-      <c r="B93" t="n">
-        <v>98595</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Bredträsk, Ång</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>681422</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7087327</v>
-      </c>
-      <c r="S93" t="n">
-        <v>5</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Isak Sarac</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Via Isak Sarac</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>129165953</v>
-      </c>
-      <c r="B94" t="n">
-        <v>98678</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Bredträsk, Ång</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>681168</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7087371</v>
-      </c>
-      <c r="S94" t="n">
-        <v>5</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Isak Sarac</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Via Isak Sarac</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10183,6 +10183,1425 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129512457</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>681428</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7087419</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129512208</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>681475</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7087319</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129511036</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>681509</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7087292</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack och födosök</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129511204</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>681531</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7087270</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129511870</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91569</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>681507</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7087471</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129512474</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>681427</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7087422</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129511062</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>681524</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7087287</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129512416</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>681453</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7087328</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129511110</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>681532</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7087283</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129511022</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>681507</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7087300</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129512325</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>681455</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7087324</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129512123</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>681453</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7087416</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129511214</v>
+      </c>
+      <c r="B105" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>681536</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7087266</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129511004</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>681512</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7087307</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10596,7 +10596,7 @@
         <v>129511870</v>
       </c>
       <c r="B97" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11602,6 +11602,210 @@
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129522735</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>681309</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7087382</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Många färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129524783</v>
+      </c>
+      <c r="B108" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>681534</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7087259</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10287,7 +10287,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129512208</v>
+        <v>129511036</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>681475</v>
+        <v>681509</v>
       </c>
       <c r="R94" t="n">
-        <v>7087319</v>
+        <v>7087292</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska ringhack och födosök</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10389,7 +10389,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129511036</v>
+        <v>129511204</v>
       </c>
       <c r="B95" t="n">
         <v>57727</v>
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>681509</v>
+        <v>681531</v>
       </c>
       <c r="R95" t="n">
-        <v>7087292</v>
+        <v>7087270</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack och födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10491,7 +10491,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129511204</v>
+        <v>129512208</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10526,10 +10526,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>681531</v>
+        <v>681475</v>
       </c>
       <c r="R96" t="n">
-        <v>7087270</v>
+        <v>7087319</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129512325</v>
+        <v>129511214</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>681455</v>
+        <v>681536</v>
       </c>
       <c r="R103" t="n">
-        <v>7087324</v>
+        <v>7087266</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11298,7 +11298,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129512123</v>
+        <v>129512325</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>681453</v>
+        <v>681455</v>
       </c>
       <c r="R104" t="n">
-        <v>7087416</v>
+        <v>7087324</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11400,7 +11400,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129511214</v>
+        <v>129512123</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>681536</v>
+        <v>681453</v>
       </c>
       <c r="R105" t="n">
-        <v>7087266</v>
+        <v>7087416</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Flera färska ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11806,6 +11806,593 @@
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129555291</v>
+      </c>
+      <c r="B109" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>681207</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7087208</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129554521</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Lämkullen, Lämkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>681458</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7086800</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129555367</v>
+      </c>
+      <c r="B111" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>681207</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7087234</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129547141</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>681443</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7087091</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>129555027</v>
+      </c>
+      <c r="B113" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Lämkullen, Lämkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>681401</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7086943</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129555316</v>
+      </c>
+      <c r="B114" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>681191</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7087217</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10596,7 +10596,7 @@
         <v>129511870</v>
       </c>
       <c r="B97" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R109" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,6 +11879,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,45 +11910,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R110" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,11 +11981,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12010,7 +12010,7 @@
         <v>129555367</v>
       </c>
       <c r="B111" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129547141</v>
       </c>
       <c r="B112" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129555316</v>
       </c>
       <c r="B114" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -11196,7 +11196,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129511214</v>
+        <v>129512123</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>681536</v>
+        <v>681453</v>
       </c>
       <c r="R103" t="n">
-        <v>7087266</v>
+        <v>7087416</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Flera färska ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11298,7 +11298,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129512325</v>
+        <v>129511214</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>681455</v>
+        <v>681536</v>
       </c>
       <c r="R104" t="n">
-        <v>7087324</v>
+        <v>7087266</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11400,7 +11400,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129512123</v>
+        <v>129512325</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>681453</v>
+        <v>681455</v>
       </c>
       <c r="R105" t="n">
-        <v>7087416</v>
+        <v>7087324</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10287,7 +10287,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129511036</v>
+        <v>129512208</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>681509</v>
+        <v>681475</v>
       </c>
       <c r="R94" t="n">
-        <v>7087292</v>
+        <v>7087319</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack och födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10389,7 +10389,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129511204</v>
+        <v>129511036</v>
       </c>
       <c r="B95" t="n">
         <v>57727</v>
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>681531</v>
+        <v>681509</v>
       </c>
       <c r="R95" t="n">
-        <v>7087270</v>
+        <v>7087292</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska ringhack och födosök</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10491,7 +10491,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129512208</v>
+        <v>129511204</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10526,10 +10526,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>681475</v>
+        <v>681531</v>
       </c>
       <c r="R96" t="n">
-        <v>7087319</v>
+        <v>7087270</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129512123</v>
+        <v>129512325</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>681453</v>
+        <v>681455</v>
       </c>
       <c r="R103" t="n">
-        <v>7087416</v>
+        <v>7087324</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11298,7 +11298,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129511214</v>
+        <v>129512123</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>681536</v>
+        <v>681453</v>
       </c>
       <c r="R104" t="n">
-        <v>7087266</v>
+        <v>7087416</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Flera färska ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11400,7 +11400,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129512325</v>
+        <v>129511214</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>681455</v>
+        <v>681536</v>
       </c>
       <c r="R105" t="n">
-        <v>7087324</v>
+        <v>7087266</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B109" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R109" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,11 +11879,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11910,45 +11905,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B110" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R110" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11981,6 +11976,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R109" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,6 +11879,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,45 +11910,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R110" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,11 +11981,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10287,7 +10287,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129512208</v>
+        <v>129511036</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>681475</v>
+        <v>681509</v>
       </c>
       <c r="R94" t="n">
-        <v>7087319</v>
+        <v>7087292</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska ringhack och födosök</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10389,7 +10389,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129511036</v>
+        <v>129511204</v>
       </c>
       <c r="B95" t="n">
         <v>57727</v>
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>681509</v>
+        <v>681531</v>
       </c>
       <c r="R95" t="n">
-        <v>7087292</v>
+        <v>7087270</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack och födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10491,7 +10491,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129511204</v>
+        <v>129512208</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10526,10 +10526,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>681531</v>
+        <v>681475</v>
       </c>
       <c r="R96" t="n">
-        <v>7087270</v>
+        <v>7087319</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129512325</v>
+        <v>129511214</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>681455</v>
+        <v>681536</v>
       </c>
       <c r="R103" t="n">
-        <v>7087324</v>
+        <v>7087266</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11298,7 +11298,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129512123</v>
+        <v>129512325</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>681453</v>
+        <v>681455</v>
       </c>
       <c r="R104" t="n">
-        <v>7087416</v>
+        <v>7087324</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11400,7 +11400,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129511214</v>
+        <v>129512123</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>681536</v>
+        <v>681453</v>
       </c>
       <c r="R105" t="n">
-        <v>7087266</v>
+        <v>7087416</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Flera färska ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B109" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R109" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,11 +11879,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11910,45 +11905,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B110" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R110" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11981,6 +11976,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10188,7 +10188,7 @@
         <v>129512457</v>
       </c>
       <c r="B93" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>129511036</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>129511204</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>129512208</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>129511870</v>
       </c>
       <c r="B97" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>129512474</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>129511062</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>129512416</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>129511110</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>129511022</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>129511214</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11298,10 +11298,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129512325</v>
+        <v>129512123</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>681455</v>
+        <v>681453</v>
       </c>
       <c r="R104" t="n">
-        <v>7087324</v>
+        <v>7087416</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Flera färska ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11400,10 +11400,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129512123</v>
+        <v>129512325</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>681453</v>
+        <v>681455</v>
       </c>
       <c r="R105" t="n">
-        <v>7087416</v>
+        <v>7087324</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11505,7 +11505,7 @@
         <v>129511004</v>
       </c>
       <c r="B106" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>129522735</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>129524783</v>
       </c>
       <c r="B108" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>129555367</v>
       </c>
       <c r="B111" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129547141</v>
       </c>
       <c r="B112" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>129555027</v>
       </c>
       <c r="B113" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129555316</v>
       </c>
       <c r="B114" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12392,6 +12392,685 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129674494</v>
+      </c>
+      <c r="B115" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>681047</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7087529</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129674701</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>680945</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7087502</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129674433</v>
+      </c>
+      <c r="B117" t="n">
+        <v>80175</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>681047</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7087529</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129674518</v>
+      </c>
+      <c r="B118" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>680976</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7087508</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129675743</v>
+      </c>
+      <c r="B119" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>681127</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7087414</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129675788</v>
+      </c>
+      <c r="B120" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>681137</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7087424</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129675994</v>
+      </c>
+      <c r="B121" t="n">
+        <v>98756</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>681146</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7087372</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -11196,7 +11196,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129511214</v>
+        <v>129512325</v>
       </c>
       <c r="B103" t="n">
         <v>57730</v>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>681536</v>
+        <v>681455</v>
       </c>
       <c r="R103" t="n">
-        <v>7087266</v>
+        <v>7087324</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11298,7 +11298,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129512123</v>
+        <v>129511214</v>
       </c>
       <c r="B104" t="n">
         <v>57730</v>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>681453</v>
+        <v>681536</v>
       </c>
       <c r="R104" t="n">
-        <v>7087416</v>
+        <v>7087266</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11400,7 +11400,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129512325</v>
+        <v>129512123</v>
       </c>
       <c r="B105" t="n">
         <v>57730</v>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>681455</v>
+        <v>681453</v>
       </c>
       <c r="R105" t="n">
-        <v>7087324</v>
+        <v>7087416</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Flera färska ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10188,7 +10188,7 @@
         <v>129512457</v>
       </c>
       <c r="B93" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10287,10 +10287,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129511036</v>
+        <v>129512208</v>
       </c>
       <c r="B94" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>681509</v>
+        <v>681475</v>
       </c>
       <c r="R94" t="n">
-        <v>7087292</v>
+        <v>7087319</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack och födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10389,10 +10389,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129511204</v>
+        <v>129511036</v>
       </c>
       <c r="B95" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>681531</v>
+        <v>681509</v>
       </c>
       <c r="R95" t="n">
-        <v>7087270</v>
+        <v>7087292</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska ringhack och födosök</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10491,10 +10491,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129512208</v>
+        <v>129511204</v>
       </c>
       <c r="B96" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10526,10 +10526,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>681475</v>
+        <v>681531</v>
       </c>
       <c r="R96" t="n">
-        <v>7087319</v>
+        <v>7087270</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10596,7 +10596,7 @@
         <v>129511870</v>
       </c>
       <c r="B97" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>129512474</v>
       </c>
       <c r="B98" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>129511062</v>
       </c>
       <c r="B99" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>129512416</v>
       </c>
       <c r="B100" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>129511110</v>
       </c>
       <c r="B101" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>129511022</v>
       </c>
       <c r="B102" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>129512325</v>
       </c>
       <c r="B103" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11298,10 +11298,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129511214</v>
+        <v>129512123</v>
       </c>
       <c r="B104" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>681536</v>
+        <v>681453</v>
       </c>
       <c r="R104" t="n">
-        <v>7087266</v>
+        <v>7087416</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Flera färska ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11400,10 +11400,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129512123</v>
+        <v>129511214</v>
       </c>
       <c r="B105" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>681453</v>
+        <v>681536</v>
       </c>
       <c r="R105" t="n">
-        <v>7087416</v>
+        <v>7087266</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11505,7 +11505,7 @@
         <v>129511004</v>
       </c>
       <c r="B106" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>129522735</v>
       </c>
       <c r="B107" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>129524783</v>
       </c>
       <c r="B108" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>129555367</v>
       </c>
       <c r="B111" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129547141</v>
       </c>
       <c r="B112" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>129555027</v>
       </c>
       <c r="B113" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129555316</v>
       </c>
       <c r="B114" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>129674701</v>
       </c>
       <c r="B116" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>129674433</v>
       </c>
       <c r="B117" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10188,7 +10188,7 @@
         <v>129512457</v>
       </c>
       <c r="B93" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10287,10 +10287,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129512208</v>
+        <v>129511036</v>
       </c>
       <c r="B94" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>681475</v>
+        <v>681509</v>
       </c>
       <c r="R94" t="n">
-        <v>7087319</v>
+        <v>7087292</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska ringhack och födosök</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10389,10 +10389,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129511036</v>
+        <v>129511204</v>
       </c>
       <c r="B95" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>681509</v>
+        <v>681531</v>
       </c>
       <c r="R95" t="n">
-        <v>7087292</v>
+        <v>7087270</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack och födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10491,10 +10491,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129511204</v>
+        <v>129512208</v>
       </c>
       <c r="B96" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10526,10 +10526,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>681531</v>
+        <v>681475</v>
       </c>
       <c r="R96" t="n">
-        <v>7087270</v>
+        <v>7087319</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10596,7 +10596,7 @@
         <v>129511870</v>
       </c>
       <c r="B97" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>129512474</v>
       </c>
       <c r="B98" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>129511062</v>
       </c>
       <c r="B99" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>129512416</v>
       </c>
       <c r="B100" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>129511110</v>
       </c>
       <c r="B101" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>129511022</v>
       </c>
       <c r="B102" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11196,10 +11196,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129512325</v>
+        <v>129511214</v>
       </c>
       <c r="B103" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>681455</v>
+        <v>681536</v>
       </c>
       <c r="R103" t="n">
-        <v>7087324</v>
+        <v>7087266</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11298,10 +11298,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129512123</v>
+        <v>129512325</v>
       </c>
       <c r="B104" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>681453</v>
+        <v>681455</v>
       </c>
       <c r="R104" t="n">
-        <v>7087416</v>
+        <v>7087324</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11400,10 +11400,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129511214</v>
+        <v>129512123</v>
       </c>
       <c r="B105" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>681536</v>
+        <v>681453</v>
       </c>
       <c r="R105" t="n">
-        <v>7087266</v>
+        <v>7087416</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Flera färska ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11505,7 +11505,7 @@
         <v>129511004</v>
       </c>
       <c r="B106" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>129522735</v>
       </c>
       <c r="B107" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>129524783</v>
       </c>
       <c r="B108" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>129555367</v>
       </c>
       <c r="B111" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129547141</v>
       </c>
       <c r="B112" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>129555027</v>
       </c>
       <c r="B113" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129555316</v>
       </c>
       <c r="B114" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>129674701</v>
       </c>
       <c r="B116" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>129674433</v>
       </c>
       <c r="B117" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R109" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,11 +11879,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11910,45 +11905,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B110" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R110" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11981,6 +11976,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10596,7 +10596,7 @@
         <v>129511870</v>
       </c>
       <c r="B97" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R109" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,6 +11879,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,45 +11910,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R110" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,11 +11981,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12010,7 +12010,7 @@
         <v>129555367</v>
       </c>
       <c r="B111" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129547141</v>
       </c>
       <c r="B112" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>129555027</v>
       </c>
       <c r="B113" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129555316</v>
       </c>
       <c r="B114" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>129674701</v>
       </c>
       <c r="B116" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>129674433</v>
       </c>
       <c r="B117" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R109" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,11 +11879,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11910,45 +11905,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B110" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R110" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11981,6 +11976,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R109" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,6 +11879,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,45 +11910,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R110" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,11 +11981,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10596,7 +10596,7 @@
         <v>129511870</v>
       </c>
       <c r="B97" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>129555367</v>
       </c>
       <c r="B111" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129547141</v>
       </c>
       <c r="B112" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129555316</v>
       </c>
       <c r="B114" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>129674701</v>
       </c>
       <c r="B116" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10596,7 +10596,7 @@
         <v>129511870</v>
       </c>
       <c r="B97" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R109" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,11 +11879,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11910,45 +11905,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B110" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R110" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11981,6 +11976,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12010,7 +12010,7 @@
         <v>129555367</v>
       </c>
       <c r="B111" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129547141</v>
       </c>
       <c r="B112" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129555316</v>
       </c>
       <c r="B114" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>129674701</v>
       </c>
       <c r="B116" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R109" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,6 +11879,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,45 +11910,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R110" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,11 +11981,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -10287,7 +10287,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129511036</v>
+        <v>129511204</v>
       </c>
       <c r="B94" t="n">
         <v>57736</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>681509</v>
+        <v>681531</v>
       </c>
       <c r="R94" t="n">
-        <v>7087292</v>
+        <v>7087270</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack och födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10389,7 +10389,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129511204</v>
+        <v>129512208</v>
       </c>
       <c r="B95" t="n">
         <v>57736</v>
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>681531</v>
+        <v>681475</v>
       </c>
       <c r="R95" t="n">
-        <v>7087270</v>
+        <v>7087319</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10491,7 +10491,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129512208</v>
+        <v>129511036</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10526,10 +10526,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>681475</v>
+        <v>681509</v>
       </c>
       <c r="R96" t="n">
-        <v>7087319</v>
+        <v>7087292</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska ringhack och födosök</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R109" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,11 +11879,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11910,45 +11905,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B110" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R110" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11981,6 +11976,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12010,7 +12010,7 @@
         <v>129555367</v>
       </c>
       <c r="B111" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129547141</v>
       </c>
       <c r="B112" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129555316</v>
       </c>
       <c r="B114" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -11808,45 +11808,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129555291</v>
+        <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>98790</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>681207</v>
+        <v>681458</v>
       </c>
       <c r="R109" t="n">
-        <v>7087208</v>
+        <v>7086800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,6 +11879,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,45 +11910,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129554521</v>
+        <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>681458</v>
+        <v>681207</v>
       </c>
       <c r="R110" t="n">
-        <v>7086800</v>
+        <v>7087208</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,11 +11981,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall, obestämd ålder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -11811,7 +11811,7 @@
         <v>129554521</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>129555291</v>
       </c>
       <c r="B110" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>129555367</v>
       </c>
       <c r="B111" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129547141</v>
       </c>
       <c r="B112" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>129555027</v>
       </c>
       <c r="B113" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129555316</v>
       </c>
       <c r="B114" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>129674701</v>
       </c>
       <c r="B116" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>129674433</v>
       </c>
       <c r="B117" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>129674701</v>
       </c>
       <c r="B116" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>129674433</v>
       </c>
       <c r="B117" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>129674701</v>
       </c>
       <c r="B116" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>129674433</v>
       </c>
       <c r="B117" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -12398,7 +12398,7 @@
         <v>129674494</v>
       </c>
       <c r="B115" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>129674701</v>
       </c>
       <c r="B116" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>129674433</v>
       </c>
       <c r="B117" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>129674518</v>
       </c>
       <c r="B118" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>129675743</v>
       </c>
       <c r="B119" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>129675788</v>
       </c>
       <c r="B120" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>129675994</v>
       </c>
       <c r="B121" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126836346</v>
+        <v>126837206</v>
       </c>
       <c r="B2" t="n">
-        <v>91491</v>
+        <v>78769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681265</v>
+        <v>680899</v>
       </c>
       <c r="R2" t="n">
-        <v>7087123</v>
+        <v>7087435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,45 +776,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126837206</v>
+        <v>126836318</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680899</v>
+        <v>681172</v>
       </c>
       <c r="R3" t="n">
-        <v>7087435</v>
+        <v>7087214</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +870,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,32 +886,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126837203</v>
+        <v>126836346</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>91480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681075</v>
+        <v>681265</v>
       </c>
       <c r="R4" t="n">
-        <v>7087404</v>
+        <v>7087123</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +971,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -981,7 +990,7 @@
         <v>126836209</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,54 +1088,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836318</v>
+        <v>126837203</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681172</v>
+        <v>681075</v>
       </c>
       <c r="R6" t="n">
-        <v>7087214</v>
+        <v>7087404</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,12 +1173,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1189,54 +1189,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836231</v>
+        <v>126836434</v>
       </c>
       <c r="B7" t="n">
-        <v>56853</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681110</v>
+        <v>681368</v>
       </c>
       <c r="R7" t="n">
-        <v>7087306</v>
+        <v>7087145</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836434</v>
+        <v>126836422</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681368</v>
+        <v>681560</v>
       </c>
       <c r="R8" t="n">
-        <v>7087145</v>
+        <v>7087320</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,45 +1391,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836422</v>
+        <v>126836231</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>681560</v>
+        <v>681110</v>
       </c>
       <c r="R9" t="n">
-        <v>7087320</v>
+        <v>7087306</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
         <v>126837209</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126837081</v>
+        <v>126836292</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>78770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,34 +1613,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>681499</v>
+        <v>681520</v>
       </c>
       <c r="R11" t="n">
-        <v>7087039</v>
+        <v>7086769</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,12 +1687,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836292</v>
+        <v>126840607</v>
       </c>
       <c r="B12" t="n">
-        <v>78777</v>
+        <v>78769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,34 +1714,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>681520</v>
+        <v>681406</v>
       </c>
       <c r="R12" t="n">
-        <v>7086769</v>
+        <v>7087115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,29 +1774,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1804,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126837205</v>
+        <v>126837081</v>
       </c>
       <c r="B13" t="n">
-        <v>78776</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1815,34 +1829,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>681270</v>
+        <v>681499</v>
       </c>
       <c r="R13" t="n">
-        <v>7087158</v>
+        <v>7087039</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,12 +1903,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1905,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126840607</v>
+        <v>126837205</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>78769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,19 +1948,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>681406</v>
+        <v>681270</v>
       </c>
       <c r="R14" t="n">
-        <v>7087115</v>
+        <v>7087158</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,40 +1987,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126840005</v>
+        <v>126840170</v>
       </c>
       <c r="B15" t="n">
-        <v>8439</v>
+        <v>80143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,34 +2031,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>681380</v>
+        <v>681446</v>
       </c>
       <c r="R15" t="n">
-        <v>7087013</v>
+        <v>7087459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,29 +2091,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2121,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126840170</v>
+        <v>126840005</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>8436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,37 +2146,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>681446</v>
+        <v>681380</v>
       </c>
       <c r="R16" t="n">
-        <v>7087459</v>
+        <v>7087013</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,40 +2203,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2236,32 +2236,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836224</v>
+        <v>126836219</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>91284</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>681282</v>
+        <v>681508</v>
       </c>
       <c r="R17" t="n">
-        <v>7087132</v>
+        <v>7087463</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126837065</v>
+        <v>126838810</v>
       </c>
       <c r="B18" t="n">
-        <v>78777</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>681401</v>
+        <v>681251</v>
       </c>
       <c r="R18" t="n">
-        <v>7087113</v>
+        <v>7086940</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,12 +2422,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2441,7 +2441,7 @@
         <v>126836435</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,32 +2539,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836219</v>
+        <v>126836224</v>
       </c>
       <c r="B20" t="n">
-        <v>91295</v>
+        <v>79600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>681508</v>
+        <v>681282</v>
       </c>
       <c r="R20" t="n">
-        <v>7087463</v>
+        <v>7087132</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126838810</v>
+        <v>126837065</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>78770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,34 +2651,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>681251</v>
+        <v>681401</v>
       </c>
       <c r="R21" t="n">
-        <v>7086940</v>
+        <v>7087113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,12 +2725,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2741,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126836225</v>
+        <v>126837055</v>
       </c>
       <c r="B22" t="n">
-        <v>58520</v>
+        <v>80018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,34 +2752,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208249</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>681499</v>
+        <v>681459</v>
       </c>
       <c r="R22" t="n">
-        <v>7087486</v>
+        <v>7087038</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,12 +2826,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126837055</v>
+        <v>126836225</v>
       </c>
       <c r="B23" t="n">
-        <v>80025</v>
+        <v>58516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,34 +2853,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>208249</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>681459</v>
+        <v>681499</v>
       </c>
       <c r="R23" t="n">
-        <v>7087038</v>
+        <v>7087486</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,12 +2927,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2946,7 +2946,7 @@
         <v>126837042</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126837217</v>
+        <v>126836432</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>681283</v>
+        <v>681386</v>
       </c>
       <c r="R25" t="n">
-        <v>7087132</v>
+        <v>7087146</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3129,12 +3129,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126836432</v>
+        <v>126837217</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>681386</v>
+        <v>681283</v>
       </c>
       <c r="R26" t="n">
-        <v>7087146</v>
+        <v>7087132</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,12 +3230,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3246,10 +3246,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836214</v>
+        <v>126836427</v>
       </c>
       <c r="B27" t="n">
-        <v>96700</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,21 +3257,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>681496</v>
+        <v>681540</v>
       </c>
       <c r="R27" t="n">
-        <v>7087506</v>
+        <v>7087272</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836427</v>
+        <v>126836214</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>96689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>681540</v>
+        <v>681496</v>
       </c>
       <c r="R28" t="n">
-        <v>7087272</v>
+        <v>7087506</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,7 +3451,7 @@
         <v>126839951</v>
       </c>
       <c r="B29" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,57 +3549,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126830094</v>
+        <v>126836297</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>78770</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>681091</v>
+        <v>681585</v>
       </c>
       <c r="R30" t="n">
-        <v>7087426</v>
+        <v>7087270</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3629,40 +3617,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3673,45 +3650,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126836297</v>
+        <v>126830094</v>
       </c>
       <c r="B31" t="n">
-        <v>78777</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>681585</v>
+        <v>681091</v>
       </c>
       <c r="R31" t="n">
-        <v>7087270</v>
+        <v>7087426</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3741,29 +3730,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3774,45 +3774,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126837072</v>
+        <v>126837194</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>57817</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>681410</v>
+        <v>681159</v>
       </c>
       <c r="R32" t="n">
-        <v>7087105</v>
+        <v>7087381</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3875,45 +3875,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836424</v>
+        <v>126837072</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>98436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>681515</v>
+        <v>681410</v>
       </c>
       <c r="R33" t="n">
-        <v>7087397</v>
+        <v>7087105</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3960,12 +3960,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3976,32 +3976,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836425</v>
+        <v>126837199</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>80143</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>681499</v>
+        <v>680957</v>
       </c>
       <c r="R34" t="n">
-        <v>7087381</v>
+        <v>7087424</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,12 +4061,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4077,32 +4077,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126837199</v>
+        <v>126836425</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680957</v>
+        <v>681499</v>
       </c>
       <c r="R35" t="n">
-        <v>7087424</v>
+        <v>7087381</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4162,12 +4162,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4178,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126837194</v>
+        <v>126836424</v>
       </c>
       <c r="B36" t="n">
-        <v>57821</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>681159</v>
+        <v>681515</v>
       </c>
       <c r="R36" t="n">
-        <v>7087381</v>
+        <v>7087397</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4263,12 +4263,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4279,53 +4279,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126837200</v>
+        <v>126836221</v>
       </c>
       <c r="B37" t="n">
-        <v>57658</v>
+        <v>91284</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>681264</v>
+        <v>681514</v>
       </c>
       <c r="R37" t="n">
-        <v>7087324</v>
+        <v>7087467</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4360,11 +4352,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4377,12 +4364,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4396,7 +4383,7 @@
         <v>126837208</v>
       </c>
       <c r="B38" t="n">
-        <v>78776</v>
+        <v>78769</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4494,45 +4481,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836221</v>
+        <v>126837200</v>
       </c>
       <c r="B39" t="n">
-        <v>91295</v>
+        <v>57654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>681514</v>
+        <v>681264</v>
       </c>
       <c r="R39" t="n">
-        <v>7087467</v>
+        <v>7087324</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,6 +4562,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4579,12 +4579,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4598,7 +4598,7 @@
         <v>126836232</v>
       </c>
       <c r="B40" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4704,59 +4704,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126836349</v>
+        <v>126840180</v>
       </c>
       <c r="B41" t="n">
-        <v>98482</v>
+        <v>80114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>681163</v>
+        <v>681446</v>
       </c>
       <c r="R41" t="n">
-        <v>7087254</v>
+        <v>7087459</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4786,29 +4775,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4819,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126840180</v>
+        <v>126836426</v>
       </c>
       <c r="B42" t="n">
-        <v>80121</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4830,37 +4830,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>681446</v>
+        <v>681490</v>
       </c>
       <c r="R42" t="n">
-        <v>7087459</v>
+        <v>7087351</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4890,40 +4887,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4934,45 +4920,59 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126836426</v>
+        <v>126836349</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>681490</v>
+        <v>681163</v>
       </c>
       <c r="R43" t="n">
-        <v>7087351</v>
+        <v>7087254</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
         <v>126836218</v>
       </c>
       <c r="B44" t="n">
-        <v>91295</v>
+        <v>91284</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>126830813</v>
       </c>
       <c r="B45" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126837207</v>
       </c>
       <c r="B46" t="n">
-        <v>78776</v>
+        <v>78769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>126837201</v>
       </c>
       <c r="B47" t="n">
-        <v>97325</v>
+        <v>97314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126837051</v>
+        <v>126836534</v>
       </c>
       <c r="B48" t="n">
-        <v>57821</v>
+        <v>78678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5460,34 +5460,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>681251</v>
+        <v>681563</v>
       </c>
       <c r="R48" t="n">
-        <v>7087107</v>
+        <v>7087315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,12 +5534,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836534</v>
+        <v>126837051</v>
       </c>
       <c r="B49" t="n">
-        <v>78685</v>
+        <v>57817</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5561,34 +5561,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>681563</v>
+        <v>681251</v>
       </c>
       <c r="R49" t="n">
-        <v>7087315</v>
+        <v>7087107</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5635,12 +5635,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5654,7 +5654,7 @@
         <v>126837040</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5752,45 +5752,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126836423</v>
+        <v>126840200</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>91480</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>681555</v>
+        <v>681091</v>
       </c>
       <c r="R51" t="n">
-        <v>7087326</v>
+        <v>7087431</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5820,29 +5823,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5853,10 +5867,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126837204</v>
+        <v>126836423</v>
       </c>
       <c r="B52" t="n">
-        <v>80121</v>
+        <v>79011</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5864,21 +5878,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5888,10 +5902,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>681057</v>
+        <v>681555</v>
       </c>
       <c r="R52" t="n">
-        <v>7087434</v>
+        <v>7087326</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5938,12 +5952,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5954,48 +5968,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126840200</v>
+        <v>126837066</v>
       </c>
       <c r="B53" t="n">
-        <v>91491</v>
+        <v>78770</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>681091</v>
+        <v>681269</v>
       </c>
       <c r="R53" t="n">
-        <v>7087431</v>
+        <v>7087084</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6025,40 +6036,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6069,10 +6069,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126837066</v>
+        <v>126837204</v>
       </c>
       <c r="B54" t="n">
-        <v>78777</v>
+        <v>80114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6080,34 +6080,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>681269</v>
+        <v>681057</v>
       </c>
       <c r="R54" t="n">
-        <v>7087084</v>
+        <v>7087434</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6154,12 +6154,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6170,10 +6170,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126836496</v>
+        <v>126837237</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>92609</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6181,21 +6181,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>681155</v>
+        <v>681451</v>
       </c>
       <c r="R55" t="n">
-        <v>7087260</v>
+        <v>7087145</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6255,12 +6255,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6274,7 +6274,7 @@
         <v>126836421</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>126837080</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126837237</v>
+        <v>126836496</v>
       </c>
       <c r="B58" t="n">
-        <v>92620</v>
+        <v>98353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>681451</v>
+        <v>681155</v>
       </c>
       <c r="R58" t="n">
-        <v>7087145</v>
+        <v>7087260</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6558,12 +6558,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6574,32 +6574,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126836431</v>
+        <v>126837210</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>98436</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>681443</v>
+        <v>681199</v>
       </c>
       <c r="R59" t="n">
-        <v>7087186</v>
+        <v>7087367</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6659,12 +6659,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6675,32 +6675,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126837230</v>
+        <v>126837211</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>98436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>680902</v>
+        <v>681207</v>
       </c>
       <c r="R60" t="n">
-        <v>7087430</v>
+        <v>7087379</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6776,32 +6776,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126837210</v>
+        <v>126836275</v>
       </c>
       <c r="B61" t="n">
-        <v>98448</v>
+        <v>97314</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>681199</v>
+        <v>681493</v>
       </c>
       <c r="R61" t="n">
-        <v>7087367</v>
+        <v>7087510</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6861,12 +6861,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6877,32 +6877,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126837211</v>
+        <v>126836431</v>
       </c>
       <c r="B62" t="n">
-        <v>98448</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>681207</v>
+        <v>681443</v>
       </c>
       <c r="R62" t="n">
-        <v>7087379</v>
+        <v>7087186</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,12 +6962,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6978,32 +6978,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126836275</v>
+        <v>126837230</v>
       </c>
       <c r="B63" t="n">
-        <v>97325</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>681493</v>
+        <v>680902</v>
       </c>
       <c r="R63" t="n">
-        <v>7087510</v>
+        <v>7087430</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7063,12 +7063,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7079,10 +7079,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126836294</v>
+        <v>126837196</v>
       </c>
       <c r="B64" t="n">
-        <v>78777</v>
+        <v>57817</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7090,21 +7090,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>681517</v>
+        <v>681047</v>
       </c>
       <c r="R64" t="n">
-        <v>7086829</v>
+        <v>7087442</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,12 +7164,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7180,10 +7180,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126837196</v>
+        <v>126837067</v>
       </c>
       <c r="B65" t="n">
-        <v>57821</v>
+        <v>78770</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7191,34 +7191,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>681047</v>
+        <v>681203</v>
       </c>
       <c r="R65" t="n">
-        <v>7087442</v>
+        <v>7087139</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7265,12 +7265,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7281,10 +7281,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126837067</v>
+        <v>126836294</v>
       </c>
       <c r="B66" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,14 +7312,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>681203</v>
+        <v>681517</v>
       </c>
       <c r="R66" t="n">
-        <v>7087139</v>
+        <v>7086829</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7366,12 +7366,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7382,32 +7382,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126837215</v>
+        <v>126836274</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>97314</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>681516</v>
+        <v>681531</v>
       </c>
       <c r="R67" t="n">
-        <v>7087367</v>
+        <v>7087468</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7467,12 +7467,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7483,32 +7483,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126836220</v>
+        <v>126837216</v>
       </c>
       <c r="B68" t="n">
-        <v>91295</v>
+        <v>79011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>681510</v>
+        <v>681451</v>
       </c>
       <c r="R68" t="n">
-        <v>7087465</v>
+        <v>7087136</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7568,12 +7568,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7584,10 +7584,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126837216</v>
+        <v>126837215</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>681451</v>
+        <v>681516</v>
       </c>
       <c r="R69" t="n">
-        <v>7087136</v>
+        <v>7087367</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7685,45 +7685,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126830801</v>
+        <v>126836220</v>
       </c>
       <c r="B70" t="n">
-        <v>78776</v>
+        <v>91284</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>681063</v>
+        <v>681510</v>
       </c>
       <c r="R70" t="n">
-        <v>7087438</v>
+        <v>7087465</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7753,19 +7753,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7780,12 +7770,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7796,10 +7786,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126836208</v>
+        <v>126830801</v>
       </c>
       <c r="B71" t="n">
-        <v>79636</v>
+        <v>78769</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7807,34 +7797,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>681523</v>
+        <v>681063</v>
       </c>
       <c r="R71" t="n">
-        <v>7086816</v>
+        <v>7087438</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7864,9 +7854,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7881,12 +7881,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7897,32 +7897,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126836274</v>
+        <v>126836208</v>
       </c>
       <c r="B72" t="n">
-        <v>97325</v>
+        <v>79629</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>681531</v>
+        <v>681523</v>
       </c>
       <c r="R72" t="n">
-        <v>7087468</v>
+        <v>7086816</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8001,7 +8001,7 @@
         <v>126836299</v>
       </c>
       <c r="B73" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>126837064</v>
       </c>
       <c r="B74" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126840611</v>
+        <v>126838812</v>
       </c>
       <c r="B75" t="n">
-        <v>78777</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8211,37 +8211,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>681406</v>
+        <v>681315</v>
       </c>
       <c r="R75" t="n">
-        <v>7087115</v>
+        <v>7086965</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8271,40 +8268,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8315,10 +8301,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126837041</v>
+        <v>126837214</v>
       </c>
       <c r="B76" t="n">
-        <v>79636</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8326,34 +8312,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>681269</v>
+        <v>681377</v>
       </c>
       <c r="R76" t="n">
-        <v>7087084</v>
+        <v>7087346</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8400,12 +8386,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8416,10 +8402,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126828689</v>
+        <v>126837041</v>
       </c>
       <c r="B77" t="n">
-        <v>57658</v>
+        <v>79629</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8427,46 +8413,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>681562</v>
+        <v>681269</v>
       </c>
       <c r="R77" t="n">
-        <v>7087373</v>
+        <v>7087084</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8496,19 +8470,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8523,12 +8487,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8539,10 +8503,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126838812</v>
+        <v>126828689</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>57654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8550,34 +8514,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>681315</v>
+        <v>681562</v>
       </c>
       <c r="R78" t="n">
-        <v>7086965</v>
+        <v>7087373</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8607,9 +8583,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8624,12 +8610,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8640,10 +8626,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126837214</v>
+        <v>126840611</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>78770</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8651,34 +8637,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>681377</v>
+        <v>681406</v>
       </c>
       <c r="R79" t="n">
-        <v>7087346</v>
+        <v>7087115</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8708,29 +8697,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8741,45 +8741,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126839934</v>
+        <v>126840136</v>
       </c>
       <c r="B80" t="n">
-        <v>79636</v>
+        <v>91284</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lamkullen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>681223</v>
+        <v>681471</v>
       </c>
       <c r="R80" t="n">
-        <v>7087108</v>
+        <v>7087265</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8809,29 +8812,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8842,10 +8856,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126841269</v>
+        <v>126836211</v>
       </c>
       <c r="B81" t="n">
-        <v>78776</v>
+        <v>91241</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8853,37 +8867,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>680900</v>
+        <v>681517</v>
       </c>
       <c r="R81" t="n">
-        <v>7087441</v>
+        <v>7086829</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8913,40 +8924,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8957,10 +8957,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126836211</v>
+        <v>126839934</v>
       </c>
       <c r="B82" t="n">
-        <v>91252</v>
+        <v>79629</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8968,21 +8968,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>681517</v>
+        <v>681223</v>
       </c>
       <c r="R82" t="n">
-        <v>7086829</v>
+        <v>7087108</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9042,12 +9042,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9058,32 +9058,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126840136</v>
+        <v>126841269</v>
       </c>
       <c r="B83" t="n">
-        <v>91295</v>
+        <v>78769</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9092,14 +9092,14 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lamkullen, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>681471</v>
+        <v>680900</v>
       </c>
       <c r="R83" t="n">
-        <v>7087265</v>
+        <v>7087441</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9173,45 +9173,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126836433</v>
+        <v>126840216</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>98436</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>681377</v>
+        <v>681171</v>
       </c>
       <c r="R84" t="n">
-        <v>7087152</v>
+        <v>7087371</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9241,29 +9249,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9274,53 +9293,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126840216</v>
+        <v>126836433</v>
       </c>
       <c r="B85" t="n">
-        <v>98448</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>681171</v>
+        <v>681377</v>
       </c>
       <c r="R85" t="n">
-        <v>7087371</v>
+        <v>7087152</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9350,40 +9361,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9397,7 +9397,7 @@
         <v>126837202</v>
       </c>
       <c r="B86" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>126837049</v>
       </c>
       <c r="B87" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>126841337</v>
       </c>
       <c r="B88" t="n">
-        <v>98365</v>
+        <v>98353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>126838801</v>
       </c>
       <c r="B89" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9821,10 +9821,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126840233</v>
+        <v>126848802</v>
       </c>
       <c r="B90" t="n">
-        <v>98484</v>
+        <v>80049</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9832,49 +9832,40 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>223621</v>
+        <v>6457</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>681171</v>
+        <v>681455</v>
       </c>
       <c r="R90" t="n">
-        <v>7087371</v>
+        <v>7087007</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9903,7 +9894,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9913,7 +9904,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9929,12 +9920,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9945,10 +9936,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126848802</v>
+        <v>126840233</v>
       </c>
       <c r="B91" t="n">
-        <v>80056</v>
+        <v>98472</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9956,40 +9947,49 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6457</v>
+        <v>223621</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Rödtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>681455</v>
+        <v>681171</v>
       </c>
       <c r="R91" t="n">
-        <v>7087007</v>
+        <v>7087371</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10044,12 +10044,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10063,7 +10063,7 @@
         <v>126829744</v>
       </c>
       <c r="B92" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -13077,7 +13077,7 @@
         <v>131126304</v>
       </c>
       <c r="B122" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>131125897</v>
       </c>
       <c r="B123" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -13077,7 +13077,7 @@
         <v>131126304</v>
       </c>
       <c r="B122" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>131125897</v>
       </c>
       <c r="B123" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -13077,7 +13077,7 @@
         <v>131126304</v>
       </c>
       <c r="B122" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>131125897</v>
       </c>
       <c r="B123" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -13077,7 +13077,7 @@
         <v>131126304</v>
       </c>
       <c r="B122" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>131125897</v>
       </c>
       <c r="B123" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -13077,7 +13077,7 @@
         <v>131126304</v>
       </c>
       <c r="B122" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>131125897</v>
       </c>
       <c r="B123" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -13077,7 +13077,7 @@
         <v>131126304</v>
       </c>
       <c r="B122" t="n">
-        <v>57892</v>
+        <v>57897</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>131125897</v>
       </c>
       <c r="B123" t="n">
-        <v>57892</v>
+        <v>57897</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 38542-2025 artfynd.xlsx
+++ b/artfynd/A 38542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY164"/>
+  <dimension ref="A1:AZ164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836214</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836533</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836534</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836535</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836304</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129674701</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,6 +1407,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836240</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,6 +1511,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836346</t>
         </is>
       </c>
     </row>
@@ -1588,6 +1633,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840200</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836211</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837237</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836218</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1992,6 +2057,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836219</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2093,6 +2163,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836220</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836221</t>
         </is>
       </c>
     </row>
@@ -2309,6 +2389,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840136</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2429,6 +2514,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828739</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2530,6 +2620,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836377</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2631,6 +2726,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836378</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2732,6 +2832,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836418</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2833,6 +2938,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836419</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2934,6 +3044,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836420</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3035,6 +3150,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836421</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3136,6 +3256,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836422</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3237,6 +3362,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836423</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3338,6 +3468,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836424</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3439,6 +3574,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836425</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3540,6 +3680,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836426</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3641,6 +3786,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836427</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3742,6 +3892,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836428</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3843,6 +3998,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836429</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3944,6 +4104,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836431</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4045,6 +4210,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836432</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4146,6 +4316,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836433</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4247,6 +4422,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836434</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4348,6 +4528,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836435</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4449,6 +4634,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836438</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4550,6 +4740,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837080</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4651,6 +4846,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837081</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4752,6 +4952,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837214</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4853,6 +5058,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837215</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4954,6 +5164,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837216</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5055,6 +5270,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837217</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5156,6 +5376,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837218</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5257,6 +5482,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837230</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5358,6 +5588,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838810</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5459,6 +5694,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838811</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5560,6 +5800,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838812</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5671,6 +5916,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126830801</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5772,6 +6022,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836313</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5873,6 +6128,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836314</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5974,6 +6234,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837205</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6075,6 +6340,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837206</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6176,6 +6446,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837207</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6275,6 +6550,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837208</t>
         </is>
       </c>
     </row>
@@ -6392,6 +6672,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840607</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6507,6 +6792,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126841269</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6604,6 +6894,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129555027</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6715,6 +7010,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126830813</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6816,6 +7116,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836207</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6917,6 +7222,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836208</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7018,6 +7328,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836209</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7119,6 +7434,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837040</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7220,6 +7540,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837041</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7321,6 +7646,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837042</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7422,6 +7752,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837043</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7519,6 +7854,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838785</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7620,6 +7960,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839934</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7726,6 +8071,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836246</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7827,6 +8177,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836254</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7926,6 +8281,11 @@
       <c r="AY72" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837055</t>
         </is>
       </c>
     </row>
@@ -8043,6 +8403,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848802</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8144,6 +8509,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837202</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8245,6 +8615,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837203</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8344,6 +8719,11 @@
       <c r="AY76" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837204</t>
         </is>
       </c>
     </row>
@@ -8461,6 +8841,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840180</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8558,6 +8943,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129674433</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8657,6 +9047,11 @@
       <c r="AY79" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837199</t>
         </is>
       </c>
     </row>
@@ -8774,6 +9169,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840170</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8897,6 +9297,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828689</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9011,6 +9416,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837200</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9112,6 +9522,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839960</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9214,6 +9629,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838791</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9316,6 +9736,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511004</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9418,6 +9843,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511022</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9520,6 +9950,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511036</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9622,6 +10057,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511062</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9724,6 +10164,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511110</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9826,6 +10271,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511204</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9928,6 +10378,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511214</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10030,6 +10485,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512123</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10132,6 +10592,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512208</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10234,6 +10699,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512325</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10336,6 +10806,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512364</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10438,6 +10913,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512457</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10540,6 +11020,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512474</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10642,6 +11127,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522735</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10744,6 +11234,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524783</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10846,6 +11341,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129554521</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10948,6 +11448,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131125897</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11050,6 +11555,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131126304</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11160,6 +11670,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836231</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11269,6 +11784,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836232</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11382,6 +11902,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837048</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11495,6 +12020,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837049</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11618,6 +12148,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126827890</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11741,6 +12276,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828321</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11842,6 +12382,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837051</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11943,6 +12488,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837194</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12048,6 +12598,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837195</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12149,6 +12704,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837196</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12246,6 +12806,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838796</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12347,6 +12912,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839951</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12448,6 +13018,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840005</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12549,6 +13124,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836225</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12650,6 +13230,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836495</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12751,6 +13336,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836496</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12850,6 +13440,11 @@
       <c r="AY119" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836497</t>
         </is>
       </c>
     </row>
@@ -12968,6 +13563,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126841337</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13083,6 +13683,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836344</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13198,6 +13803,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836348</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13313,6 +13923,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836349</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13426,6 +14041,11 @@
       <c r="AY124" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836350</t>
         </is>
       </c>
     </row>
@@ -13553,6 +14173,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126829744</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13677,6 +14302,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126830094</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13783,6 +14413,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836305</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13893,6 +14528,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836318</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14003,6 +14643,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836322</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14113,6 +14758,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836331</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14214,6 +14864,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837072</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14315,6 +14970,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837209</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14416,6 +15076,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837210</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14515,6 +15180,11 @@
       <c r="AY134" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837211</t>
         </is>
       </c>
     </row>
@@ -14637,6 +15307,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840216</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14762,6 +15437,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840329</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14859,6 +15539,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129547141</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14956,6 +15641,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129555291</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15053,6 +15743,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129555316</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15150,6 +15845,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129555367</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15247,6 +15947,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129674494</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15344,6 +16049,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129674518</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15441,6 +16151,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675743</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15538,6 +16253,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675788</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15635,6 +16355,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675994</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15736,6 +16461,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836274</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15837,6 +16567,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836275</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15938,6 +16673,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837201</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16062,6 +16802,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840233</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16163,6 +16908,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836292</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16264,6 +17014,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836294</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16365,6 +17120,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836295</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16466,6 +17226,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836297</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16567,6 +17332,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836298</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16668,6 +17438,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836299</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16769,6 +17544,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837063</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16870,6 +17650,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837064</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16971,6 +17756,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837065</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17072,6 +17862,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837066</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17173,6 +17968,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837067</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17270,6 +18070,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838801</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17385,6 +18190,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840611</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17486,6 +18296,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836339</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17587,8 +18402,178 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836224</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>